--- a/sql/歌詞成型_完成形入力_FRUITSZIPPER_v2.xlsx
+++ b/sql/歌詞成型_完成形入力_FRUITSZIPPER_v2.xlsx
@@ -1,33 +1,49 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="完成形入力" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="現在の歌詞(参考)" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="完成形入力" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="現在の歌詞(参考)" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="4">
     <font>
-      <name val="Calibri"/>
+      <name val="ＭＳ Ｐゴシック"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="128"/>
+      <family val="3"/>
       <b val="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="128"/>
+      <family val="3"/>
+      <sz val="6"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="128"/>
+      <family val="3"/>
+      <sz val="11"/>
     </font>
   </fonts>
   <fills count="2">
@@ -50,12 +66,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -418,12 +440,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C42"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:D42"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
     <col width="80" customWidth="1" min="3" max="3"/>
+    <col width="70" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -454,7 +477,13 @@
         </is>
       </c>
     </row>
-    <row r="5"/>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>※「完成形入力」シートのD列に、現在の歌詞モーダルで実際に表示されている内容（lyric_col/col_space適用済み、セクション変わり目は空行）を1曲1セルで追記しました。見比べて完成形を入力してください。</t>
+        </is>
+      </c>
+    </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
@@ -471,27 +500,116 @@
           <t>完成形歌詞</t>
         </is>
       </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
+      <c r="D6" s="1" t="inlineStr">
+        <is>
+          <t>現在のモーダル表示(参考)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="409.5" customFormat="1" customHeight="1" s="2">
+      <c r="A7" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>BABY I LOVED</t>
         </is>
       </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>It's time to live my life 雨音
+It's time to live my life ため息
+Baby I loved, Baby I loved
+儚くって あれほど信じた日々の終点
+水たまりの街 反射するメモリー
+やけに、綺麗、憎い。
+Baby I loved, Baby I loved
+わがままって　恋から愛への証拠だった
+解釈違いの　ロマンス手を振って
+それじゃ、私、行くね。
+湾岸ルーレット　ハイウェイ
+乗り込んだら　もうどこへだって行けそう
+夜が明ける頃は　違う私で
+そうよ悲しまないで
+顔を上げて
+そんなに惨めじゃないでしょ？
+すこし すこしずつ変われるチャンス
+It's time to live my life. 雨音
+It's time to live my life ため息
+Baby I loved, Baby I loved
+猫かぶって　合わせて笑うの疲れちゃった
+今更　泣きついたって
+無駄よ　許してあげない
+きっと　きっと　きっとよ
+湾岸ルーレット　ハイウェイ
+乗り込んだら　もうどこへだって行けそう
+夜が明ける頃は　違う私で
+そうよ悲しまないで
+顔を上げて
+そんなに惨めじゃないでしょ？
+すこし　すこしずつ変われるチャンス
+湾岸ルーレット　ハイウェイ
+涙にそっと　都会のネオンを映す
+きらり　まとい　素敵　大人になれる
+そうよ　悲しまないで感じるでしょ　予感
+今が
+ここが
+彼が
+雨の
+夜が
+すこし　すこしずつ変われるチャンス</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>It's time to live my life 雨音
+It's time to live my life ため息
+Baby I loved, Baby I loved
+儚くってあれほど信じた日々の終点
+水たまりの街 反射するメモリー
+やけに、綺麗、憎い。
+Baby I loved, Baby I loved
+わがままって
+恋から愛への証拠だった
+解釈違いの ロマンス手を振って
+それじゃ、私、行くね。
+湾岸ルーレット ハイウェイ
+乗り込んだら もうどこへだって行けそう
+夜が明ける頃は 違う私で
+そうよ悲しまないで 顔を上げて
+そんなに惨めじゃないでしょ？
+すこし すこしずつ変われるチャンス
+It's time to live my life. 雨音
+It's time to live my life ため息
+Baby I loved, Baby I loved
+猫かぶって合わせて笑うの疲れちゃった
+今更泣きついたって無駄よ 許してあげない
+きっと きっと きっとよ
+湾岸ルーレット ハイウェイ
+乗り込んだら もうどこへだって行けそう
+夜が明ける頃は 違う私で
+そうよ悲しまないで 顔を上げて
+そんなに惨めじゃないでしょ？
+すこし すこしずつ変われるチャンス
+湾岸ルーレット ハイウェイ
+涙にそっと 都会のネオンを映す
+きらり まとい 素敵 大人になれる
+そうよ悲しまないで 感じるでしょ 予感
+今が ここが 彼が 雨の 夜が
+すこし すこしずつ変われるチャンス</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="409.5" customFormat="1" customHeight="1" s="2">
+      <c r="A8" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>CO-個性</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>こ、個性
 こーこーせい
@@ -576,30 +694,218 @@
 こ、個性
 こーこーせい
 こ、個性
+こーこーせい
+こ、個性
 こーこーせい</t>
         </is>
       </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>こ、個性
+こーこーせい
+同じ制服着ても
+こ、個性
+こーこーせい
+同じ授業受けても
+こ、個性
+こーこーせい
+同じ頃生まれても
+こ、個性
+こーこーせい
+同じとこ続いても
+わたしはわたしで、いーの
+ってそりゃそうです、
+でもきょうはきょうの協調性も
+求められるような恋とか、なんとか欲しがられたりだけど
+個性の方向性が
+虹色くらいにあって、大変です
+ねぇ、だから気持ち悪さもかわいいでしょ？
+ねぇ、あきらめの悪さもかわいいでしょ？
+こ、個性
+こーこーせい
+同じ制服着ても
+こ、個性
+こーこーせい
+同じように生きても
+発揮したいね
+君の変なところが好きです
+わたしと違う君がいるから
+むずがゆいような言葉だって今、言っていこ？
+say yeah
+大事なことは一個
+say yeah
+時々は笑うこと
+オリジナルなこう世界を
+どうやったって見せるのです
+君のそんなとこ世界一好き
+え、こーこーせい？
+ハイスクールスチューデント？
+いや、それキャラクター？
+とりあえずバイブス高い方でいきたい
+え、いつからだっていいじゃん、いつまでとかないじゃん
+卒業するまで、しないけどね
+ひたすら気ままでいーの
+はまあ三年、
+ほらきょうは
+きょうの小テストをクリアしとかなきゃね
+ほんとはまったく気にしてもいないけれど
+顔面の偏差値なんて
+自分の中でしかなくて、参考程度
+ねぇ、ねえねえ昨日よりもかわいいでしょ？
+ねぇ、ねえって言いすぎてもかわいいでしょ？
+こ、個性
+こーこーせい
+同じ制服着ても
+こ、個性
+こーこーせい
+同じように生きても
+君の変なところが好きです
+昨日と違う君がいるから
+忘れないような言葉も何度も、言っていこ？
+say yeah
+大事なことは一個
+say yeah
+私が言ったってこと
+オリジナルなこう世界を
+どうやったって生きるのです
+君と
+君の変なところが好きです
+わたしと違う君がいるから
+むずがゆいような言葉だって今、言っていこ？
+say yeah
+大事なことは一個
+say yeah
+時々は笑うこと
+オリジナルなこう世界を
+どうやったって見せるのです
+君のそんなとこ世界一好き
+こ、個性
+こーこーせい
+こ、個性
+こーこーせい
+こ、個性
+こーこーせい
+こ、個性
+こーこーせい</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="409.5" customFormat="1" customHeight="1" s="2">
+      <c r="A9" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>Going!</t>
         </is>
       </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Going・Going・Going・Going・Going・Going
+フルッパー (Hey)
+ステージにハードに溢れるバブり
+生まれたまんまでClap ya hands
+Jumping・Jumping・Jumping・Jumping・Jumping・Jumping
+踊りだしますか？？
+狭しい世界のVS常識
+今日は主役だ Party Party Party
+（FRUITS ZIPPER！）
+最強メンタリティ この現在地
+押すだけじゃないの？ Enterキー
+本音チラつかす Zip up！ Zip down！
+何度だって失敗したい
+逃がすなチャンスを(チャンスを)
+へー、それってあなたの感想？(イイじゃん！)
+このドキドキは何でしょう？ 恋の万華鏡？
+ま、知らんけど (Ah Ha Ha Ha Ha Ha！)
+ビバ異端児　そうさ個性が大事
+たまによそみしてたら置いてかれるから
+（ちゅ！ ちゅ！ チューモク）
+飛び出し注意　なんて無視して「今夜こそ！」
+（踊ろう踊ろう踊ろう）
+「ねぇ踊って？」
+マイナス掛けたらプラスって知ってる？
+弱虫同士でいーじゃん
+賞味期限明日の仲でいい
+ほんとかマジかは後にして
+いっさいがっさい弱音はポポイポーイ
+ここでもう一言いいですか～？
+いいよ～～↑
+もうチュードク (Hey↓) 不満幾千億 (Hey↓)
+日本列島七転八倒して We're alive
+超モードク(Hey↓) ぶっちゃけのモード(ふぉ～　ふぉ～う)
+理不尽に不信　変われるぜ Cool Cool Lady
+もうチュードク(Hey↓) やばい重症ロック (Hey↓)
+かなり葛藤でも滑走して We can fly
+はいチューモク(はーい↑) きっかけは今日も(ふぉ～　ふぉ～う)
+円陣で自信　増し増しで Cool Cool Lady
+Going・Going・Going・Going・Going・Going
+フルッパー (Hey)
+ゲートリバーブに感じるバブり
+生まれる前からフォローミー Yo
+ディスコ・ディスコ・ディスコ・ディスコ・
+ディスコ・ディスコ　ディスコミュニケーション
+熱弁・詭弁もごっちゃのジョーシキ
+聴いてくれなきゃ　嫌ーね　嫌ーね　嫌ーね
+（FRUITS ZIPPER！）
+ウザいくらいのカンフル剤
+個性とコスメのギャングスタ
+自尊ヴァイヴス激アゲ中な
+負ける気がせん！ なんちゅーか！
+ソウル・香港・ロンドンに・パリに
+ブラジル・ニューヨーク・バンクーバー
+満腹中枢バグったLove 地球ZipしてTaxiったら
+人生正味どれだけなのよTell Me
+守りすぎてばっかじゃモチベーションもダウン
+（ちゅ！ ちゅ！ チューモク）
+時は金なり　まだ見ぬ世界で今夜だけ！
+歌おう歌おう歌おう
+「ねぇ歌って？」
+やる気も勇気もそこそこで
+シンデレラなんてズルすぎてチート
+別にそんなんうらやまくしくないし
+人畜無害の顔ですが
+ほんとは野心ありよりのありっぽーい
+さらにもう一言いいですか～？
+いいよ～～↑
+もうチュードク(Hey↓) 不満幾千億(Hey↓)
+日本列島七転八倒して We're alive
+超モードク(Hey↓) ぶっちゃけのモード(ふぉ～　ふぉ～う)
+理不尽に不信　変われるぜ Cool Cool Lady
+もうチュードク(Hey↓) やばい重症ロック(Hey↓)
+かなり葛藤でも滑走して We can fly
+はいチューモク(はーい↑) きっかけは今日も(ふぉ～　ふぉ～う)
+円陣で自信　増し増しで Cool Cool Lady
+Going・Going・Going・Going・Going・Going
+フルッパー (Hey)
+ステージにハードに溢れるバブり
+生まれたまんまでClap ya hands
+Jumping・Jumping・Jumping・Jumping・Jumping・Jumping
+踊りだしますか？？
+狭しい世界のVS常識
+愛はバルクだ Pump Up Pump Up Pump Up
+Going・Going・Going・Going・Going・Going
+フルッパー (Hey)
+ゲートリバーブに感じるバブみ
+生まれる前からフォローミー Yo
+ディスコ・ディスコ・ディスコ・ディスコ・
+ディスコ・ディスコ　ディスコミュニケーション
+熱弁・詭弁もごっちゃのジョーシキ
+聴いてくれなきゃ　嫌ーね・嫌ーね・嫌ーね
+（FRUITS ZIPPER！）</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="409.5" customFormat="1" customHeight="1" s="2">
+      <c r="A10" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>JAM</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>let's jam！
 Ja ja ja ja la ja la jam
@@ -692,17 +998,110 @@
 Ja ja ja ja la ja la jam</t>
         </is>
       </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>let's jam！
+Ja ja ja ja la ja la jam
+Ja ja ja ja la ja la jam
+果物不足の世界でも
+欲しいタイプの甘さはある
+そうして手にした宝物
+ずっとそこに置いておきたいけど
+時々ちょっとめんどうな瞬間あったり
+何が普通？or 平均？比べたりもして
+友達同士、知らないおしゃれをしてみたり
+この手を離す日も来る
+それまでは
+君にべったりしちゃったり
+おしつけちゃうラベルとかも
+確かめ合えれば、たぶんあり
+ジャム選んだり、好き語ったり
+そんな朝ごはん食べたら
+はじめちゃいましょうか？
+ねえここから世界へ
+史上最高の君のかわいさを伝えたいよ、baby baby
+だって毎日、愛は生きてる、ご機嫌に
+前途洋々の君のかわいさを伝えたいよ、baby baby
+ふたり好きな歌、歌って
+(let's jam)
+Ja ja ja ja la ja la jam
+賞味期限のないラブです
+Ja ja ja ja la ja la jam
+でも少しはあせりたいです
+Ja ja ja ja la ja la jam
+君にも世界にも、今ひとつ
+言っておかなきゃいけない
+ねえ、どうしようか、それなら、
+じゃあじゃあじゃあ 「君が好き」
+(let's jam)
+Ja ja ja ja la ja la jam
+Ja ja ja ja la ja la jam
+情報多めな時代でも
+なぜか目につく苦さがある
+だけども見えない宝物
+それが大事、忘れずいたいのに
+時々ちょっと煮詰まることとかあったり
+それが普通？いやできない？比べたりもして
+お隣同士だからズレたりもするけど
+この手をつなぐ時には
+やさしくね
+君にぴったりしちゃったり
+無理を言っちゃうレベルとかも
+愛の裏返し、てゆうか表
+パフェ作ったり、チョコもあったり
+ジャムっちゃうような幸せから
+かみしめちゃいましょうか
+世界へ
+史上最高の君のかわいさを伝えたいよ、baby baby
+だって毎日、愛が増えてく、ご機嫌に
+前途洋々の君のかわいさを伝えたいよ、baby baby
+みんな好きなダンス踊って、
+踊って！
+Ja ja ja ja la ja la jam
+Ja ja ja ja la ja la jam
+Ja ja ja ja la ja la jam
+Ja ja ja ja la ja la jam
+せーの
+YEAH！
+ずっと大切にしてね
+でもとっておきすぎないでね
+もっといっぱい言ってね
+でも使いすぎないでね
+きっと明日も会えるね
+でも明後日も会えるね
+今日も君に会えたら
+史上最高の君のかわいさを伝えたいよ、baby baby
+だって毎日、愛は生きてる、ご機嫌に
+前途洋々の君のかわいさを伝えたいよ、baby baby
+ふたり好きな歌、歌って
+(let's jam)
+Ja ja ja ja la ja la jam
+賞味期限のないラブです
+Ja ja ja ja la ja la jam
+でも少しはあせりたいです
+Ja ja ja ja la ja la jam
+君にも世界にも、今ひとつ
+言っておかなきゃいけない
+ねえ、どうしようか、それなら、
+じゃあじゃあじゃあ 「君が好き」
+Ja ja ja ja la ja la jam
+Ja ja ja ja la ja la jam
+Ja ja ja ja la ja la jam
+Ja ja ja ja la ja la jam
+Ja ja ja ja la ja la jam</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="409.5" customFormat="1" customHeight="1" s="2">
+      <c r="A11" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>KawaiiってMagic</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
         <is>
           <t>きっと大丈夫　大丈夫
 つまずいても　涙 Bye-bye
@@ -748,77 +1147,452 @@
 Kawaii Kawaii Kawaii</t>
         </is>
       </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>きっと大丈夫　大丈夫
+つまずいても　涙 Bye-bye
+Kawaii Kawaii Kawaii
+きっと大丈夫　大丈夫
+手をつないで　涙 Bye-bye
+Ah-ah Kawaii KawaiiってMagicだわ
+夢をあきらめないで
+遠くても会おうよ　未来で
+キラキラ光る空へ
+勇気のかけら集めて
+いくよ (yeah)
+きっと大丈夫　大丈夫
+つまずいても　涙 Bye-bye
+Kawaii Kawaii Kawaii
+きっと大丈夫　大丈夫
+手をつないで　涙 Bye-bye
+Ah-ah Kawaii KawaiiってMagicだわ
+夢をあきらめないで
+いつかきっと　笑おう　未来で
+パチパチ光る星で
+勇気のかけら見つけて
+Kawaii？ Kawaii？ Kawaii？
+Kawaii？ Kawaii？ Kawaii？
+大丈夫？
+大丈夫
+きっと大丈夫　大丈夫
+つまずいても　涙 Bye-bye
+Kawaii Kawaii Kawaii
+きっと大丈夫　大丈夫
+手をつないで　涙 Bye-bye
+Ah-ah, kawaii, kawaii, kawaii (yeah)
+きっと大丈夫　大丈夫
+つまずいても　涙 Bye-bye
+きっと大丈夫　大丈夫
+Kawaii KawaiiってMagicだわ
+きっと大丈夫　大丈夫
+手をつないで　涙 Bye-bye
+Ah-ah Kawaii KawaiiってMagicだわ
+Kawaii Kawaii Kawaii
+Kawaii Kawaii Kawaii
+Kawaii Kawaii Kawaii
+Kawaii Kawaii Kawaii</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="409.5" customFormat="1" customHeight="1" s="2">
+      <c r="A12" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>NEW KAWAII</t>
         </is>
       </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>（せーの）
+ららららららららららら
+wow wow wow wow wow wow
+新しい！
+パンダ的な雰囲気もいいよね （いいよね）
+白黒はっきりつけたいような、時代じゃない？
+お姫様な扱いもいいよね （もちろんいいよね）
+寝起きはしばらくパジャマでいたいけど、仕方がない？
+ぜったいぜったいキャラじゃないって
+スタンプで返事したくなるような、やばいお誘い
+投票して決めるそれって
+ぜんぜんきゅーとじゃないじゃん
+わたしこのままでもいいじゃん
+愛、未来、おかし、メイク、友達、笑顔、睡眠、
+ほらぜんぶ大切だね
+さ、アップデートしよ？
+大好きな人が、にゅーかわいかった
+それがほんの少しでも、わたしのせいならいいな
+おしもおされぬ、愛が見つかる
+嬉しくなりすぎる新しさです
+update、update したデートで
+oh oh oh oh oh oh 全員参加で
+a new world a new world そんなワードで
+大事なことを言い合いましょう
+さあかわいいも言い合いましょう？
+新しい？
+どっちでもない雰囲気もいいよね？ （いいよね）
+あかしろはっきり決まらないけどいいじゃない
+王子様は未定でもいいよね （もちろんいいよね）
+わたしが王様とかでもいいじゃん、がんばります
+ぜったいぜったいありえないって
+スタンスもくずしたくなるような、グレートな世界
+多数決で決めるなんて
+ぜんぜんきゅーとじゃないじゃん
+わたし少数派でいいじゃん
+愛、別の愛、また別の愛、それ以外の愛、
+ほらぜんぶ大切だね
+ねえ、アップデートしよ？
+大好きな人が、にゅーかわいかった
+それがほんの少しでも、自分のためならいいな
+誰かが決めたものでもなくて
+そうしたいからする、過ごし方です
+update update したデートで
+oh oh oh oh oh oh 自由参加で
+a new world a new world そんなワードで
+大事な人を褒め合いましょう
+wow wow wow wow wow wow
+wow wow wow wow wow wow
+wow wow wow wow wow wow
+wow wow wow wow wow wow
+大好きな人が、にゅーかわいかった
+それがほんの少しでも、明日を照らせばいいな
+おしもおされぬ、愛が見つかる
+未来しかないこの感じ (好き！)
+大好きな人が、にゅーかわいかった
+それがほんの少しでも、わたしのせいならいいな
+おしもおされぬ、愛が見つかる
+嬉しくなりすぎる新しさです
+update、update したデートで
+oh oh oh oh oh oh 全員参加で
+a new world a new world そんなワードで
+大事なことを言い合いましょう
+さあかわいいも言い合いましょう？</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="409.5" customFormat="1" customHeight="1" s="2">
+      <c r="A13" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>RADIO GALAXY</t>
         </is>
       </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>超次元　まじまじ
+セカイに走るセンセーション
+満天の星ぎゅっと抱きしめ旅に出よう
+全宇宙巻き込んでいっちょ突破
+刺されインテンション
+めーいっぱいにとばせ
+電波（レディオ）ギャラクシー
+GO GO GO LET'S GO
+ARE YOU READY？ GALAXY
+いくぞ！
+わああああああああ
+FRUITS ZIPPER！！
+せーのほいほいほい
+…あーよいしょー！
+当たり前に日が昇り
+新たな時代カミン
+光の速さでグッモーニン
+あれあれ待てよと言う間に
+日常も色チェンジ
+カラフルさながらファンタジー
+想像じゃなくて
+確かにここにある
+脳に染みてく好奇心のトキメキ
+楽しいこと　一緒に感じたいの
+こぼさないで　ちゃんと受け取ってさ！
+アアア　チェック　ワンツー　で途切れる交信中？
+ノッティスミー！マッシュ！マッシュ！マッシュ！
+スマッシュかませよー
+ボタンを倍プッシュ
+炸裂する猛ラッシュ
+技もスルーなキミに届けたいの
+繋がれ点と点結んで線と線
+この指とまれ　でせーので返事！はーい！！！
+みんなまとめて最高へ招待
+これが我らの煌煌のショータイム！
+ああ　超次元　まじまじ
+セカイがゆれるハイテンション
+満天の星ずっと照らすよどこまでも
+全宇宙巻き込んでいっせーので
+ステキ　フォーメーション☆
+めーいっぱいにとばせ
+電波（レディオ）ギャラクシー
+-緊急事態発生-
+人口過多定員オーバー？
+昔は皆兄弟だった？
+手と手を繋げよ友よ
+胸を張って生きれば　最強なんだ
+瞳の真ん中　ブラックホールみたいだね
+予想もつかないような　何かしたい
+不可能の文字　オモイで吹き消したら
+何度でも　さぁ
+歌うんだ　（大きな声で）
+あなたに　（届けたいから）
+あなたに　（伝えたいから）
+強くほら
+GO GO GO LET'S GO  ARE YOU READY？
+超次元まじまじ
+セカイに走るセンセーション
+満天の星ぎゅっと抱きしめ旅に出よう
+全宇宙巻き込んでいっちょ突破
+刺されインテンション　めーいっぱいにとばせ
+進め未来へ
+ラララ…</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="409.5" customFormat="1" customHeight="1" s="2">
+      <c r="A14" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>Re→TRY &amp; FLY</t>
         </is>
       </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>滔々語ってるそのユメは大胆な
+“挑戦”,“冒険”
+荒唐無稽かな
+情状酌量の余地アリと判断です
+OK,OK
+ムジナだよね
+すんすん泣いている懐古中迷子の
+手を引いて
+落ちるリアル
+淡々整頓して本音絞ったら
+まだ、まだ、まだ夢の途中だ
+ああ意味ないや ラルラリラッタ
+祈り飽きて
+不完全でも飛ばずにいられなくて――
+Retry
+さぁボクとキミの白地図を彩る青い生き様
+重ねれば示す場所
+奇跡の在り処
+Fly high
+そうそれはそれは待たずに迎えに行くんだよ
+同じほう見つめ
+Re→TRY &amp; FLY
+喧喧囂囂のクリエイティブ・ワールド
+（warning x4）
+大丈夫 ここは光射す
+ただ、ただ、ただ実力主義
+もう寝ちゃいたいな
+ラルラリラッタ
+これもボクさ
+不完全燃焼 甘んじてないで今――
+Retry
+さぁその眼その手 ボク達はゆめゆめ忘るるなかれ
+あどけなくいたいけな
+仮面（マスク）裏返せ
+Fly high
+変わらない魂照らしあう どんな夜も
+同じほう見つめ
+Re→TRY &amp; FLY
+ここは遠く遠く描いた場所 鼓動の音色を標せ
+ああ 一人一人違う果実を手にして
+軌跡を結んで
+Retry
+さぁボクとキミの白地図を彩る青い生き様
+重ねれば示す場所
+奇跡の在り処
+Fly high
+そうそれはそれは待たずに迎えに行くんだよ
+同じほう見つめどこまでも
+ひとりじゃないよ
+Re→TRY &amp; FLY</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="409.5" customFormat="1" customHeight="1" s="2">
+      <c r="A15" s="2" t="n">
         <v>13</v>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>skyfeelan</t>
         </is>
       </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>みんなでステージで1番かわいく輝けるように
+明日地球が終わっちゃっても
+大丈夫なくらい幸せそうでしょ？
+（見てて）
+ストレスで買ったお洋服たちは
+今日も影から見守ってくれてるよ
+長いようで早かったここまでを詰め込んで
+楽しいが届くように私がんばります！
+駆け抜けろskyfeelan さらに加速して
+目が合えばなんでもわかるくらい 大好きだよ
+飛んでいけskyfeelan ここのみんな巻き込んで
+向かう場所は一緒がいいな
+もっと可愛く見えるようにたくさん研究します♡
+緊張で泣きそうだけど特別になる予感がする
+世界中に届いてけ！！
+文字数足りない溢れる愛
+たくさん込めて歌って踊るよ
+（見てて）
+やってみたかったがいっぱいつまってる
+今の私の一番大事な場所
+可愛くね なるように工夫して歌ったり
+緊急事態でも歌っちゃう！？完璧主義で♡
+どこまでもskyfeelan 高く飛べそうだ
+戻って止まってた分をもっと進まなきゃね！
+ついてきてskyfeelan 夢の花が咲くまで
+私たちは諦めない
+アイドルやるまで死ねないと思って
+私##運命のドアを開いたの（私）
+駆け抜けよう
+私たちskyfeelan 想いを重ねて
+困ってたら これからも助け合っていこうな
+飛んでいけskyfeelan ここのみんな巻き込んで
+どこまでも進めちゃいそうじゃん
+成長してる私たちをもっと感じて欲しいの
+ありがとうを伝えなければ！本当に皆様ありがとう！
+キセキをずっと見ていてね！！
+Wow oh oh！</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="409.5" customFormat="1" customHeight="1" s="2">
+      <c r="A16" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>Sugarless GiRL</t>
         </is>
       </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>甘い愛には 罠があるのよ
+Wonder girl グッドモーニング
+今日も声かける
+笑いかけて 誘い出して
+キミの心は シュガーレスガール
+きっと 今どこかで 最悪な事があって
+ため息 ついてるキミ
+沁みるミュージック
+ベースのライン
+きっと 世の中の せいにしても変わんない
+それよりも 聴いてたいのは
+こんなミュージック 吹き飛ばした
+灰色の雲と雲の間に
+わずかに差し込む 光はミュージック
+何もかも上手く行けそうな 気がする程じゃない
+甘い愛には 罠があるのよ
+Wonder girl グッドモーニング
+今日も声かける
+笑いかけて 誘い出して
+キミの心は シュガーレスガール
+きっと 今どこかで 最悪な事があって
+ため息 ついてるキミ
+沁みるミュージック
+ベースのライン
+きっと 世の中の せいにしても変わんない
+それよりも 聴いてたいのは
+こんなミュージック 吹き飛ばした
+灰色の雲と雲の間に
+わずかに差し込む 光はミュージック
+何もかも 上手く行けそうな 気がする程じゃない
+甘い愛には 罠があるのよ
+Wonder girl グッドモーニング
+今日も声かける
+笑いかけて 誘い出して
+キミの心は シュガーレスガール
+lalala lalala lalala...
+シュガーレスガール</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="409.5" customFormat="1" customHeight="1" s="2">
+      <c r="A17" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>We are Frontier</t>
         </is>
       </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>いくぜ大航海 進め精一杯
+集めるSpotlight
+運命の共同体 本気の等身大
+魅せるDay and night
+Let's go さぁ出掛けよう大海原へ
+型にはハマらない集まった新時代のスター
+鮮やかに焼き付ける憧れのImageを
+与えたい私という存在を
+迫るEmbark 爆ぜろReal Anchorを解き放て
+絶対
+誰が何を言っても媚びない逃げない揺るがない
+自分らしさ磨き続けよう
+立ち上がれWe are Frontier 地図は自分で描け
+先頭は譲らない
+開港の瞬間　帆を揚げ進む Right now
+天変地異巻き起こすOnly one
+どんな未来でも切り拓くから
+君と一緒に
+搭乗手続きはした？ 新天地へご招待
+巻き込んでいく君も船出の目撃者さ
+鮮やかに裏切って期待以上のShowを
+頑張りは隠すのがクールでしょ？
+しぶき上げ荒れ狂うWaves　手懐けてみせる
+All Right
+もしも先が暗くても私が光になる
+夢を共に掴むクルーズ
+ありのままWe are Frontier 限界なんて決めるな
+迷ってるヒマはない
+狭い価値観捨てて進めRight now
+羅針盤はこの胸の中
+どんな未来でも楽しめるのは
+君がいるから
+いくぜ大航海 進め精一杯
+集めるSpotlight
+運命の共同体 本気の等身大
+魅せるDay and night
+そう乱反射する 可能性を掴むImage
+忘れない もしも波に呑まれても
+迫るEmbark 弾けろSynapse
+Anchorを解き放て
+Go on
+この瞬間切り取って1ページ書き込もう
+命懸けの冒険譚に
+闇の先にあるのはきっと希望の地平
+1歩を前へ
+波間へと噛みついて嵐さえ越えていく
+今こそ本能を呼び覚ませ
+立ち上がれWe are Frontier 戻れないけど大丈夫？
+サヨナラはしてきてね
+開演の瞬間　君の瞳をRock on
+疾風怒濤に正面切ってOn and on
+理想の未来へ
+信じた道を 思うままに 切り拓こう
+君と一緒に
+Lalalala….</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="409.5" customFormat="1" customHeight="1" s="2">
+      <c r="A18" s="2" t="n">
         <v>17</v>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>うぇるかむとぅ〜ざ♡ふるっぱー！</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
         <is>
           <t>Say　ハロー！ 上々！ どんなんご所望？
 うぇるかむとぅ～ざ FRUITS ZIPPER
@@ -881,17 +1655,80 @@
 遊ぼうぜ Brand new world！</t>
         </is>
       </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>Say　ハロー！ 上々！ どんなんご所望？
+うぇるかむとぅ～ざ FRUITS ZIPPER
+始まるストーリー　世界攻略！ さぁ、行こう！
+やっぱ NEW KAWAII じゃない？
+「まずは優衣ちゃん！」
+5秒あれば　好きにさせます。
+アイドルからの推し　目指してます。
+あっちもこっちも　＃ゆいわずらい
+10年前線！ 振りまいてるの　七福神スマイル
+「ゆいとデートしよ？」
+「つづいては、まなふぃ～！」
+みてよ！ せくしぃ　あの子ダンシンクイーン
+原宿ラブ　ガチなモンスターガール
+マジ真面目すぎ？ あいさつ欠かさん！
+ポニテ揺らして　本日もよろしく～？
+「おねがいっ...しまーーーす！」
+Say　ハロー！ HARAJUKUへ行こう！
+お好きに Pick It FRUITS ZIPPER
+超本気(まじ) なんです！ 燦然到来　あつまれ！
+最強の七色じゃない？
+「末っ子登場！ ノエル～！」
+堂々最年少　ちゅるんとDOLLY EYES
+気まぐれだね　ふんわりLIKE A CAT
+マルチリンガル 多彩な才　ドイツエンジャパン
+わぁ～るどワイドな末っ子ちゃん
+「I love you Guys～」
+「はいはい～お次は天音！」
+3度の飯　カラオケ　すき！
+アイドルオタク　ステージだいすき！
+サバサバなツンデレーション　実は涙もろいって
+みんな知ってますか～！？
+「ラーメンもつ鍋、すいとーよ」
+Say　ハロー！ 上々！ どんなんご所望？
+うぇるかむとぅ～ざ FRUITS ZIPPER
+感じる？ パッション　愛心送信　とどけて！
+全世界　魅せちゃうんじゃない？
+「おいで～かれん～！」
+泣き虫でも　めげない努力
+妹気質？ 実は長女です！
+マカロンボイスで奔走中
+期待してね♪ すくすくまつかれ　成長中～！
+「はーい！ 一生懸命がんばりまーす」
+「せーの、やっぴー！るなぴー！」
+みんなを照らす　パリピポジティブ
+完璧主義で☆派手にGALピ
+人間国宝目指すの　ふるっぱー's歌姫(ディーヴァ)
+毎日　夏仕様のハッピネス
+「もっともーっと愛してぴーや！」
+「ラストは、おすず～！」
+たらこLIP　超マイペース
+宇宙規模に　引き寄せてる
+元気印をあげちゃう　みんなにパワー！
+締めの一発ギャグ、おねがい～
+「フルーツ　ジーッ... (今私はあなたのの心をガン見しています) パァ！」
+Say　ハロー！ HARAJUKUへ行こう！
+お好きに Pick It FRUITS ZIPPER
+ぜんぶ揃った　百果繚乱　カラふる
+やっぱ NEW KAWAII じゃない？
+遊ぼうぜ Brand new world！</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="409.5" customFormat="1" customHeight="1" s="2">
+      <c r="A19" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>かがみ</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C19" s="2" t="inlineStr">
         <is>
           <t>んー、おはよ
 朝起きてまず確認
@@ -981,17 +1818,107 @@
 かわいくなりすぎちゃったんです</t>
         </is>
       </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>んー、おはよ
+朝起きてまず確認
+きょうもいい感じだね
+一年365日
+わたしのこと一番みてるひと
+好きですと、言えるのは
+当たり前とかじゃない
+一日86400秒
+ずっと付き合ってくんだから
+ママから聞いたことあるわ
+似た人を好きになるんじゃなくて、
+好きな人には似るものらしいです、
+本当です
+みんな思ったことあるわ
+目を開けたら違う自分になって
+いやいやもっと真剣に
+変身します
+ますかるのゆあ　ふるふるる
+あれ？
+かわいくなりすぎちゃったかも
+さすがに盛りすぎちゃったかも
+あなたのマネしたんです、
+だって超大好きなんだから
+かがみよかがみ、もうちょっとだけ
+かわいくなってもいいのかな？
+いつだって正直にいって、
+それで
+ひみつひみつひみつのかわいこちゃんにはなれない
+そんなことぜんぶお見通しです、
+だって逆に
+ひみつひみつひみつはわたしたちにはいらない
+だけどあなたがひみつにしたいほど
+かわいくなりすぎちゃったかも
+んーうーん
+朝起きて、そうだ休み
+やりたいことありすぎ
+1日は24時間
+っていうけど、ずっと起きてるわけでもない
+帰ったらまた確認
+当たり前とかじゃない
+とにかく自分を大事にしましょう
+ずっと付き合ってくんだから
+ママから聞いたことあるわ
+22時から2時は寝るのがよくて
+18時以降は食べないほうがいいです、
+いや無理です
+みんな思ったことあるわ
+寝てる間に変わらないのかな
+いやいややっぱ真剣に
+変身したい！
+ますかるのゆあ　ふるふるる
+あれ？
+かわいくなりすぎちゃっていい？
+ほんとに盛りすぎちゃっていい？
+あなたのこと好きです、だって超前向きなんだから
+かがみよかがみ、もうちょっとだけ
+かわいくなってもいいのかな？
+いつだって正直にいって！
+もう
+大好きです、大好きです
+って目の前の君にいっていいのかな？
+自分で言います、魔法をかけます
+嘘でもかかったふりしてね
+でもわたしもあなたも嘘がつけない
+そういうやつだから、さ
+ますかるのゆあ　ふるふるる
+あれ？
+かわいくなりすぎちゃっていい？
+ほんとに盛りすぎちゃっていい？
+あなたのこと好きです、だって超前向きなんだから
+かがみよかがみ、もうちょっとだけ
+かわいくなってもいいのかな？
+いつだって正直にいって！
+あれ？
+かわいくなりすぎちゃったかも
+さすがに盛りすぎちゃったかも
+あなたのマネしたんです、だって超大好きなんだから
+かがみよかがみ、もうちょっとだけ
+かわいくなってもいいのかな？
+いつだって正直にいって、
+それで
+ひみつひみつひみつのかわいこちゃんにはなれない
+そんなことぜんぶお見通しです、だって逆に
+ひみつひみつひみつはわたしたちにはいらない
+だけどあなたがひみつにしたいほど
+かわいくなりすぎちゃったんです</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="409.5" customFormat="1" customHeight="1" s="2">
+      <c r="A20" s="2" t="n">
         <v>19</v>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>キミコイ</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
         <is>
           <t>My sweet heart, my sweet heart,
 lovely you are like a sunshine
@@ -1057,17 +1984,83 @@
 lovely Destiny lover</t>
         </is>
       </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>My sweet heart, my sweet heart,
+lovely you are like a sunshine
+君を待っていた
+そう　出会ってわかったんだ
+何もかも映えないエビデイ
+突如　現れし王子様
+君が笑えば
+「キュン！」ってハートがしゃべるんだ
+きっと “すきぴ” や “推し” を
+超えた運命的存在
+笑っちゃうくらいカラフルな
+恋のフィルター越しの世界
+Let's share love
+Let's share love
+君と
+「ぜったい運命だよ！」
+あふれだす　あふれだす
+巡り会えた喜びが
+好きすぎる
+愛しすぎる
+これって…神様！？
+24時を回っても
+解けない魔法があるよ
+超バズしちゃうくらい
+あちあちな恋をしよう
+Destiny love
+好きバレしてもシェアしたい
+脳内でリピってるラブソング
+Let's share love
+Let's share love
+君と
+「ねぇ、ちゃんと目見て？」
+あふれだす　あふれだす
+見つめ合えばドキドキが
+祝福の鐘のようにDing Dong
+ハピネスじゃん！
+24時間経ってもずっと　消えないストーリーだよ
+君だけのあしあと
+尊くて心でスクショした
+運命は決められた物語じゃなく
+愛する強さの名前
+だから赤い糸や
+ガラスの靴が　なくたって見つけ合えたんだ
+もう私を離さないで
+あふれだす　あふれだす
+想いを今　届けよう
+好きすぎる
+愛しすぎる
+あれれ？はにかんだ？
+100年後も　きっと来世も
+好きだと言い切れるよ
+「一瞬」も「永遠」も
+君にだけ恋をしよう
+Destiny love
+My sweet heart, my sweet heart,
+Lovely you are like a sunshine
+My sweet heart, my sweet heart,
+lovely Destiny lover
+My sweet heart, my sweet heart,
+lovely you are like a moonlight
+My sweet heart, my sweet heart,
+lovely Destiny lover</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="409.5" customFormat="1" customHeight="1" s="2">
+      <c r="A21" s="2" t="n">
         <v>20</v>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>さん</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C21" s="2" t="inlineStr">
         <is>
           <t>君のこと昨日より少しだけ
 丁寧に呼んでみたら
@@ -1122,17 +2115,72 @@
 ほんとありがとさん</t>
         </is>
       </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>君のこと昨日より少しだけ
+丁寧に呼んでみたら
+なんだか幸せになりました
+日曜日、もちろん楽しみだけど
+今日もみんな呼んでるから
+なんだか幸せになりました
+天気予報に並んだ
+傘を数えるよりも
+一緒に見上げてみたらさ
+あたたかい
+みんな
+さんさんさんなんです
+太陽です
+笑顔とか、笑い声だって
+歌おう
+さんさんさんなんです
+大切です
+人が人を、君が君を、輝かせるよ
+ほんとありがとさん
+二人でもほんと嬉しいけれど
+もう一人誘ってみたら
+なんだか幸せになりました
+いつの日か、家族が増えたりして
+そんな想像してみたら
+なんだか幸せになりました
+天気予報のすぐ後
+占いがちょっときびしい
+そんなときもこの世界は
+あたたかい
+みんな
+さんさんさんなんです
+太陽です
+素顔とか、小さな声だって
+歌おう
+さんさんさんなんです
+ＯＫです
+人が人を、君が君を、認めていくよ
+ほんとありがとさん
+みんな
+さんさんさんなんです
+太陽です
+笑顔とか、笑い声だって
+みんな
+さんさんさんなんです
+太陽です
+素顔とか、小さな声だって
+歌おう
+さんさんさんなんです
+大切です
+人が人を、君が君を、輝かせるよ
+ほんとありがとさん</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="409.5" customFormat="1" customHeight="1" s="2">
+      <c r="A22" s="2" t="n">
         <v>22</v>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>スターライト・ヴァルキリー</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C22" s="2" t="inlineStr">
         <is>
           <t>「愛してください」と心臓
 差し出して生きるの　もういいの
@@ -1208,17 +2256,93 @@
 スターライト・ヴァルキリー</t>
         </is>
       </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>「愛してください」と心臓
+差し出して生きるの　もういいの
+私が私であること
+抱きしめた　ただそれだけ
+求められる最強も
+どこにでもある最強も
+みんなが手にした武器では
+立てないや　ただそれだけ
+傷つけないと　いつかこのまま
+傷つけられると　カルマ終わらない
+この星の外へ今　ついて来たいなら
+私だけ見て
+流星の剣(つるぎ)に硝子(がらす)の鎧(よろい)
+誰にも屈しない　戦わないまま
+守り抜くからね　心という結晶(クリスタル)
+カケラ…スターライト・ヴァルキリー
+メテオに乗れ　乙女よ
+誓えよ　乙女よ
+恐れるもの　振り解いて
+ときめきだけがすべて　光を信じて
+二度と負けない　ヴァルキリー
+私、カケラ…スターライト・ヴァルキリー
+願い事の破片と
+乙女心を握りしめれば
+私たちはいつでも
+燦然と光っていられるでしょう
+強くなったのではありません
+きらめきを信じているのです
+「許してください」と低頭(ていとう)
+無罪を請(こ)われても　ねぇきっと
+私は天使じゃないから
+さよならね　ただ　それだけ
+誰かを裏返して揃えて
+正しくあろうだなんてまちがい
+何を信じればいい？　とにかく駆けるさ
+私だけ見て
+流星の剣(つるぎ)に硝子(がらす)の鎧(よろい)
+誰にも屈しない　戦わないまま
+守り抜くからね　心というクリスタル
+カケラ…スターライト・ヴァルキリー
+メテオに乗れ　乙女よ
+誓えよ　乙女よ
+恐れるもの　ふり解いて
+ときめきだけがすべて　光を信じて
+二度と負けない　ヴァルキリー
+私、カケラ…スターライト・ヴァルキリー
+前世は姫でした
+今世は私で、来世も私でしょう
+このかわいいの剣は
+何人(なんぴと)たりとも傷つけず、夢物語を貫くのです
+私は天使でも女神でもなく、ただ君の善き友人
+透明の鎧の下には、とっておきのドレス
+私は、かしずかない、薙ぎ倒さない
+そして…負けない
+好きなものがあるの　ただそれだけ
+疑わないでいいの　ただまっすぐ　前
+抱きしめてたいの　友情という反射(リフレクション)
+すべて連れてゆくから
+私なら…
+流星の剣(つるぎ)に硝子(がらす)の鎧(よろい)
+誰にも屈しない　戦わないまま
+守り抜くからね　心という結晶(クリスタル)
+カケラ…スターライト・ヴァルキリー
+メテオに乗れ　乙女よ
+誓えよ　乙女よ
+恐れるもの　振り解いて
+ときめきだけがすべて　光を信じて
+二度と負けない　ヴァルキリー
+私、カケラ…スターライト・ヴァルキリー
+瞳の奥の祈り　叶えて
+私は砕けない
+スターライト・ヴァルキリー</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="409.5" customFormat="1" customHeight="1" s="2">
+      <c r="A23" s="2" t="n">
         <v>23</v>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>ずっと、ずっと、ずっと！</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C23" s="2" t="inlineStr">
         <is>
           <t>とまらない
 切ないほどに　いとおしい
@@ -1260,17 +2384,59 @@
 伝えるよ　今　“アイラブユー”</t>
         </is>
       </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>とまらない
+切ないほどに　いとおしい
+アイの告白(メロディー)
+「わたしだけ、きゅんっとさせてよ！」 って…まだ、隠したまま
+雪　のち　恋予報
+キラキラ眩しく光るんだって
+言えない気持ちと　ねぇ同じくらい　しゅんっと消えちゃうんだって
+「そんなん...だめっ！」
+あと 3cmくらい？
+ふたりの距離　もう溶かしたいよ
+ぴったりひっついて
+キミ。体温　感じたいの
+「だいじょぶ？ 寒くないの？」って意識してない？ TT みたい急接近ですっ
+顔もみれない
+困らせてばっかじゃ
+どうしよう　これ以上
+ずっと　ずっと　前から　ずっと　ずっと　ずっと
+キミが...好きでしたっ！
+その瞳(め)でぎゅっと　染められちゃってみたいの
+ドキドキがゆずれない「わたしだけ見て！」
+KOI・SHI・TE・RU ベイビー！ MY LOVE
+なんて　妄想するだけの未来？気づいてくれないかなぁ
+長いまつ毛とあざといリップの女友達(あのこたち)
+先越されたらNO...こっち向いてよ！
+鈍感過ぎ！ でも好き不意打ち　どきゅん　バキュン！　狙い撃ちですっ
+ほんと...今夜も眠れない
+テンション！どんどん高鳴ってる
+純真！輝いて舞い降りたんだ「大好き。」が　もう少し....近くで
+勇気をください
+心に積もる　あまいあまい　このキモチに
+嘘はつけないの　もうすぐ　溢れちゃいそうだ！
+ずっと　ずっと　前から　ずっと　ずっと　ずっと
+キミが...好きでしたっ！
+その手で　ぎゅっと　抱きしめられてみたいの
+ドキドキがゆずれない「わたしだけ見て！」
+AI・SHI・TE・RU べイビー！ MY LOVE
+なんて　想像してるだけじゃない
+伝えるよ　今　“アイラブユー”</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="409.5" customFormat="1" customHeight="1" s="2">
+      <c r="A24" s="2" t="n">
         <v>25</v>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>ハートのローラーコースター</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C24" s="2" t="inlineStr">
         <is>
           <t>誰かが泣きそうな夜は
 満天の星をそっと届けてあげよう
@@ -1327,17 +2493,74 @@
 波打つ　ハートのローラーコースター</t>
         </is>
       </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>誰かが泣きそうな夜は
+満天の星をそっと届けてあげよう
+未来へ描く軌跡は(Shooting Stars)
+波打つ　ハートのローラーコースター|
+La la la la 走れ
+La la どこまでも
+La la la la 先へ
+繋がる光
+La la la la 進め
+La la どこへでも
+La la la la 行こう
+We are FRUITS ZIPPER！！ YEAH！！
+急展開でもオーライ
+喜怒哀楽　気分Up and Down
+物語の途中じゃん！？
+楽しむチャンス！？
+Take it easyだって
+奇想天外is サプライズ
+ドキドキしちゃうほど自由に旅したい
+ルールなんて決めたら
+NONO
+思い切り叫べよ
+せーの
+はい！ はい！ はい！
+もっと
+はい！ はい！ はい！
+To the next→
+クールだって決めつけないで
+エンジンは全開
+Let's Gol
+はい！ はい！ はい！
+もっと
+はい！ はい！ はい！
+大変よくできました
+がんばってるキミの笑顔
+守ってあげたいな
+幾千の可能性を超えて
+キミを連れて行くよ
+どこまでも行けるどこへでも行ける
+遥か彼方へ続く
+ハートのローラーコースター
+La la la la 走れ
+La la どこまでも
+La la la la 先へ
+繋がる光
+La la la la 進め
+La la どこへでも
+La la la la 行こう
+We are FRUITS ZIPPER
+誰かが泣きそうな夜は
+満天の星を　そっと届けてあげよう
+未来へ描く軌跡は(Shooting Stars)
+波打つ　ハートのローラーコースター</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="409.5" customFormat="1" customHeight="1" s="2">
+      <c r="A25" s="2" t="n">
         <v>26</v>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>はちゃめちゃわちゃライフ！</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C25" s="2" t="inlineStr">
         <is>
           <t>ぷりぷりぷりっと　プリプリプリティー
 はぴはぴはぴっと　ハピハピハッピー
@@ -1408,17 +2631,89 @@
 はちゃめちゃわちゃっと Wah！どぅわちゃらいっ！</t>
         </is>
       </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="n">
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>ぷりぷりぷりっと　プリプリプリティー
+はぴはぴはぴっと　ハピハピハッピー
+ぶらぶらぶらっと　ブラブラブラボー
+はちゃめちゃわちゃっとWah！どぅわちゃらいっ！
+ポポポポップでホップでジップなEveryday
+はーい　さあみんなあそぼうこの指止まれ
+ウィットにとんでユニークなAnytime
+チャーミングにみんな今日もいい感じ(Fu)
+お腹が空いたらご飯を食べて
+遊び疲れたら夢の中
+カワイイとこもおバカなとこも
+ぎゅっと愛するべき推しポイントだゾ
+はちゃめちゃわちゃライフ！Wah！どぅわちゃらいっ！
+おどけたほっぺがぷりっとプリティー
+はちゃめちゃわちゃライフ！Wah！どぅわちゃらいっ！
+お茶目に生きるのだ
+はちゃめちゃわちゃライフ！Wah！どぅわちゃらいっ！
+笑って毎日はぴっとハッピー
+はちゃめちゃわちゃライフ！Wah！どぅわちゃらいっ！
+仲良く生きるのだ
+ぷりぷりぷりっと　プリプリプリティー
+はぴはぴはぴっと　ハピハピハッピー
+ぶらぶらぶらっと　ブラブラブラボー
+はちゃめちゃわちゃっとWah！どぅわちゃらいっ！
+優しい君も Do what you like
+元気な君も Do what you want
+照れ屋な君も Do what you love
+どんな君もどぅわどぅわどぅわちゃらいっ！
+毎日　毎毎日 Do what you like(Fu Fu)
+大好き　大大好き Do what you like(Fu Fu)
+胸がいっぱい　いっぱい Do what you like(Fu Fu)
+なんか照れちゃうな　どぅわどぅわどぅわちゃらいっ！
+お兄さんもお姉さんもわちゃライフ！わちゃライフ！
+呑気もお天気もわちゃライフ！わちゃライフ！
+3にも4にもわちゃライフ！わちゃライフ！
+今日もドキがムネムネ
+はちゃめちゃわちゃライフ！Wah！どぅわちゃらいっ！
+パワフル元気にほほいっとコメディー
+はちゃめちゃわちゃライフ！Wah！どぅわちゃらいっ！
+真っ直ぐに生きるのだ
+はちゃめちゃわちゃライフ！Wah！どぅわちゃらいっ！
+なんでもかんでもちゃちゃっとイージー
+はちゃめちゃわちゃライフ！Wah！どぅわちゃらいっ！
+首尾よく生きるのだ
+得意も不得意も　得手も苦手も全部君のチャームポイント
+晴れのち雨も　雨のち晴れもどっちだって構わない
+はちゃめちゃわちゃライフ！Wah！どぅわちゃらいっ！
+明日も明後日もその先もずーっとここで待ち合わせだよ
+はちゃめちゃわちゃライフ！Wah！どぅわちゃらいっ！
+忘れないでね　君と僕とのお約束
+はちゃめちゃわちゃライフ！Wah！どぅわちゃらいっ！
+なんだか夕日がいつもより綺麗だなあ
+はちゃめちゃわちゃライフ！Wah！どぅわちゃらいっ！
+ずっと一緒に生きるのだ
+じゃ、そゆことで
+(Yeah！)
+はちゃめちゃわちゃライフ！Wah！どぅわちゃらいっ！
+おどけたほっぺがぷりっとプリティー
+はちゃめちゃわちゃライフ！Wah！どぅわちゃらいっ！
+お茶目に生きるのだ
+はちゃめちゃわちゃライフ！Wah！どぅわちゃらいっ！
+笑って毎日はぴっとハッピー
+はちゃめちゃわちゃライフ！Wah！どぅわちゃらいっ！
+仲良く生きるのだ
+ぷりぷりぷりっと　プリプリプリティー
+はぴはぴはぴっと　ハピハピハッピー
+ぶらぶらぶらっと　ブラブラブラボー
+はちゃめちゃわちゃっとWah！どぅわちゃらいっ！</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="409.5" customFormat="1" customHeight="1" s="2">
+      <c r="A26" s="2" t="n">
         <v>27</v>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>ハピチョコ</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C26" s="2" t="inlineStr">
         <is>
           <t>はっぴー新年
 そろそろ考えなくちゃ
@@ -1486,17 +2781,85 @@
 ごほうびをあげたい</t>
         </is>
       </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="n">
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>はっぴー新年
+そろそろ考えなくちゃ
+みんながちょっとうるさいし
+まずは作戦会議
+おっけー元年
+今からはじまる
+ラブストーリーとか、そんなんじゃないし
+本命なんだし
+今日が本番なんてうそうそ
+大事なのはここから一ヶ月でじれったいな
+大人になったって、ドキドキしてたいもんだって
+両思いの先払い
+うんっとっ
+あまいあまいあまいあまいの
+すきすきすきすき
+っていう私が選んだ君はとびきりのスイート
+あまいあまいあまいあまい
+一年で一番の贅沢でもしちゃいましょうよ
+ちょっちょちょっと
+ちょこっとは予算とカロリーとかはオーバーでもね
+ちょっちょちょっとチョコレート、
+わたしの恋とかに
+ごほうびをあげたい
+もう今日だって！
+だいたいは決めました
+ご自宅用ですか？
+ってなんでわかったの？
+そうでもやっぱ
+みんなそわそわしちゃうの
+そりゃそうだけどね、余裕見せたら
+それも変かな
+ねえ呼び出しなんてなになに？
+きょうのところは帰って楽しみたいのにな
+でもあれわたしが、ほしかったかわいいやつじゃない？
+気になる、これ片思い？
+まって
+あまいあまいあまいあまいの
+すきすきすきすき
+そんなわたしにあなたがくれたとびきりのサプライズ
+やばいやばいやばいやばい
+そんなこと想像もしてなかったの、眠れないね
+一ヶ月も悩むなんて
+そんなの無理じゃない？
+私、毎日が本命全力
+そういうのが好きでごめん
+うんっとっ
+あまいあまいあまいあまいの
+すきすきすきすき
+っていう私が選んだ君はとびきりのスイート
+あまいあまいあまいあまい
+一年で一番の贅沢でもしよ
+うんっとっ
+あまいあまいあまいあまいの
+すきすきすきすき
+っていう私が選んだ君はとびきりのスイート
+あまいあまいあまいあまい
+一年で一番の贅沢でもしちゃいましょうよ
+ちょっちょちょっと
+ちょこっとは予算とカロリーとかはオーバーでもね
+ちょっちょちょっとチョコレート、
+わたしの恋とかに
+ごほうびをあげたい
+わたしの今日からに
+ごほうびをあげたい</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="409.5" customFormat="1" customHeight="1" s="2">
+      <c r="A27" s="2" t="n">
         <v>28</v>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
         <is>
           <t>ピポパポ</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C27" s="2" t="inlineStr">
         <is>
           <t>ピポパポパーティー
 NEW KAWAII MAGIC
@@ -1599,20 +2962,127 @@
 NEW! NEW! NEW! KAWAII!!</t>
         </is>
       </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="n">
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>ピポパポパーティー
+NEW KAWAII MAGIC
+ピポパポパーティー
+NEW KAWAII MAGIC
+ピポパポパーティー
+NEW KAWAII MAGIC
+ピポパポパーティー
+NEW KAWAII MAGIC
+ピポパ　って言うだけで
+え、ハッピー
+みんな集まれば NEW KAWAII
+世界がうらやむ大発見
+ナイショの合言葉
+(ピポパポリーン!)
+キラキラ　まぶしくて
+ついつい　ウィンクしちゃう
+ちぐはぐなこのワールド
+カラフルだね
+(レッツゴー)
+いつまでも　(も!)
+どこまでも　(も!)
+なによりも　(も!)
+だれよりも　(も!)
+止まらない
+やばい!
+ピポパポパーティー
+NEW KAWAII MAGIC
+ピポパポパーティー
+あそびましょ!
+NEW KAWAII　ってなーに
+知りたくなーい？
+もーっともっともっとおかわりちょうだい
+ピポパポパーティー
+NEW KAWAII MAGIC
+ピポパポパーティー
+みんないいね
+すごいね！OK！
+（すごいね！OK！）
+なんでもかんでもかわいいんだもん
+ちょ、まって
+ちょ、まって
+ちょ、まって　今
+世界で一番可愛いんじゃない!？
+えっらーい!
+あまネキ!にゃんこPPER!
+ノエちゃん!インテリPPER!
+ゆいちゃん!笑顔PPER!
+おすず!たらこPPER!
+まつかれ!ほっぺPPER!
+まなふぃ!きんにくPPER!
+るなぴ!ギャルPPER!
+わたしたち FRUITS ZIPPER!
+This quiet revolution of selfhood
+It is not about becoming what the world finds KAWAII
+But about discovering what makes you whole
+It's more than a style, it is a mirror
+This is NEW KAWAII.
+YEEEEAAAAHHHH!!!!!!!
+ピポパポパーティー
+NEW KAWAII MAGIC
+ピポパポパーティー
+あそびましょ!
+すごいね！OK！
+（すごいね！OK！）
+ねぇねぇ、みんなで唱えちゃお
+反抗期でも NEW KAWAII
+甘え上手は NEW KAWAII
+食べ過ぎちゃっても NEW KAWAII
+メソメソしてても NEW KAWAII？
+1年365日 NEW KAWAII
+つまずいちゃっても NEW KAWAII
+元気があれば NEW KAWAII
+生きてるだけで NEW KAWAII
+ピポパポパーティー
+NEW KAWAII MAGIC
+ピポパポパーティー
+NEW KAWAII MAGIC
+ピポパポパーティー
+NEW KAWAII MAGIC
+ピポパポパーティー
+あそびましょ!
+NEW KAWAII　ってなーに
+知りたくなーい？
+もーっともっともっと　おかわりちょうだい
+ピポパポパーティー
+NEW KAWAII MAGIC
+ピポパポパーティー
+みんないいね
+すごいね！OK！
+（すごいね！OK！）
+なんでもかんでも　かわいいんだもん
+ちょ、まって
+ちょ、まって
+ちょ、まって　今
+え、まって
+え、まって
+え、まって　今
+世界で一番可愛いんじゃない!？
+えっらーい!
+NEW! NEW! NEW! KAWAII!!
+NEW! NEW! NEW! KAWAII!!
+NEW! NEW! NEW! KAWAII!!</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="409.5" customFormat="1" customHeight="1" s="2">
+      <c r="A28" s="2" t="n">
         <v>29</v>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>ぴゅあいんざわーるど</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C28" s="2" t="inlineStr">
         <is>
           <t>We Are FRUITS ZIPPER！
 いっちょ！ひい！ふう！みー！よー！
+ぴゅあいんざわーるど！
 ぴゅあいんざわーるど！
 Yes！Yes！NEW KAWAII
 レペゼン原宿 We're fromジャパン
@@ -1625,7 +3095,7 @@
 っていうか今ここ何処？何時何分？
 What Happened！？
 たまにふと「足りない…足りない…」焦燥感…
-ん～「間違い？」「間違いないような…？」
+ん〜「間違い？」「間違いないような…？」
 ほら考え出したらキリがないから付き合いきれないわ！
 だけど毎回毎回向き合って
 この一回一回を声張って
@@ -1665,7 +3135,7 @@
 近いようですね…
 ぴゅあいんざわーるど！
 超超絶好調！時には少々絶望よ？
-そんなUP&amp;DOWN　繰り返しながら
+そんなUP＆DOWN　繰り返しながら
 てんてこ舞いの毎日
 少年と少女　いつかのような青春を
 それを純粋だって
@@ -1700,17 +3170,109 @@
 ぴゅあいんざわーるど！</t>
         </is>
       </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="n">
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>We Are FRUITS ZIPPER！
+いっちょ！ひい！ふう！みー！よー！
+ぴゅあいんざわーるど！
+ぴゅあいんざわーるど！
+Yes！Yes！NEW KAWAII
+レペゼン原宿 We're fromジャパン
+そんな我ら7人は人呼んで
+一富士、二鷹、
+FRUITS ZIPPER！
+日々ドンブラコドンブラコ
+激流　予測不可能に身を任せ
+あれ？どっちなの？どっちなの？
+っていうか今ここ何処？何時何分？
+What Happened！？
+たまにふと「足りない…足りない…」焦燥感…
+ん〜「間違い？」「間違いないような…？」
+ほら考え出したらキリがないから付き合いきれないわ！
+だけど毎回毎回向き合って
+この一回一回を声張って
+「なれたらいいな」じゃなくて「なるんです！！」私たちは
+いつも一緒だよっ
+ぴゅあいんざわーるど！天地海越えて届け遠くまで
+この世はもっと美しいのだ純粋だ
+ぴゅあいんざわーるど！言語さえ越えて響けこのメロディ
+僕らの夢詰め込んだこの世界は
+世界は
+世界はさ…
+ぴゅあいんざわーるど！
+ぴゅあいんざわーるど！
+(日本全土 World Wide)
+桁外れの野望 笑うのは野暮
+(日本全土 World Wide)
+太陽系銀河系にSay Hello
+(日本全土 World Wide)
+言霊を信じているからこそ
+(日本全土 World Wide)
+どデカい事　ハッタリかましてこう
+荒波にのってサーフィンのように
+流れ流されて今何処に？
+あっぷあっぷで乗り切ったワンウィーク
+日月火水木金土曜日
+Don't worry we are homie
+もうやってらんない時は適当に
+見てる阿呆より踊る阿呆に
+鬼さんこ〜ちら
+手の鳴る方に
+さあさあおいで
+ぴゅあいんざわーるど！ドキドキいっぱいこの手の中に
+誰だって持ってるダイヤモンドの原石だ
+ぴゅあいんざわーるど！ワクワクばっか見渡せる限り
+どうやら目指していたとこは近いようです
+近いようです
+近いようですね…
+ぴゅあいんざわーるど！
+超超絶好調！時には少々絶望よ？
+そんなUP＆DOWN　繰り返しながら
+てんてこ舞いの毎日
+少年と少女　いつかのような青春を
+それを純粋だって
+ホンモノだって
+言うのなら今すぐ
+取り返してやるのさ
+ぴゅあいんざわーるど…元々胸の奥にあるの
+傷ついた分が満たされるようもう一度
+ぴゅあいんざわーるど…まだ何者でもない私だけど
+一歩一歩ずつ歩んでいった将来に
+将来に
+将来にさ…
+迎えにきたよっ
+ぴゅあいんざわーるど！天地海越えて届け遠くまで
+この世はもっと美しいのだ純粋だ
+ぴゅあいんざわーるど！言語さえ越えて響けこのメロディ
+僕らの夢詰め込んだこの世界は
+世界は
+世界はさ…
+ぴゅあいんざわーるど！
+LIFE IS THE PURENESS！LIFE IS THE PURENESS！
+純粋も不透明もヒューマニティー
+LIFE IS THE PURENESS！LIFE IS THE PURENESS！
+私たちを繋いでいる輪
+LIFE IS THE PURENESS！LIFE IS THE PURENESS！
+純粋も不透明もヒューマニティー
+LIFE IS THE PURENESS！LIFE IS THE PURENESS！
+私たちを繋いでいる輪
+最後にみんなでいっせーのせっ！
+We Are FRUITS ZIPPER！
+いっちょ！ひい！ふう！みー！よー！
+ぴゅあいんざわーるど！</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="409.5" customFormat="1" customHeight="1" s="2">
+      <c r="A29" s="2" t="n">
         <v>31</v>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
         <is>
           <t>フルーツバスケット</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C29" s="2" t="inlineStr">
         <is>
           <t>聞いたことありませんか？
 世界は椅子取りゲームだって
@@ -1764,17 +3326,71 @@
 ああ、美しく育った空よりまぶしい、恋よりまぶしい人生</t>
         </is>
       </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="n">
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>聞いたことありませんか？
+世界は椅子取りゲームだって
+でも実際は
+立ってても良い、床に座っても良い
+そんな感じ
+今が旬って、言葉に迷って
+動き出せなかったり、あるある
+またそれだって、味変みたいねって
+いえる今です、さんきゅー
+そして、どんなときもパフェみたいに可愛く集まっていたいけど
+苦い顔の時だってある
+でも変わらない事実
+主役は君
+everyday　だれもみんな
+それぞれの甘酸っぱさを持って生きてる
+それがなんであっても、実になってるんだから
+愛される、今日も
+everyday　君といれば
+そのままでも変わっても良いって知ってる
+ああ、美しく育った空よりまぶしい、恋よりまぶしい人生
+誰も彼も相性ってやつに
+感情を持ってかれる
+悩むならbaby
+ミックスジュースで
+みんな一緒になっちゃっていい
+結局、どういう関係だってお互い次第
+籠の中でも自由にやればいい
+食わず嫌いって、言葉を覚えて
+動き出せなかったり、あるある
+でもそれだって、違うかもねって
+いえる人なんです、好き
+ほんとに好き
+everyday　だれもみんな
+それぞれの甘酸っぱさを持って生きてる
+たまにそれに飽きても、保存して未来で
+愛されるだろう
+everyday　君がいれば
+生きているそれだけで良いって知ってる
+ああ、限りなく透明な空より尊い、恋より尊い運命
+そして、どんなときもパフェみたいに可愛く集まっていたいけど
+苦い顔の時だってある
+でも変わらない事実
+主役は君
+everyday　だれもみんな
+それぞれの甘酸っぱさを持って生きてる
+それがなんであっても、実になってるんだから
+愛される、今日も
+everyday　君といれば
+そのままでも変わっても良いって知ってる
+ああ、美しく育った空よりまぶしい、恋よりまぶしい人生</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="409.5" customFormat="1" customHeight="1" s="2">
+      <c r="A30" s="2" t="n">
         <v>32</v>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>ふるっぱーりー！</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="C30" s="2" t="inlineStr">
         <is>
           <t>Yeah! Yeah! Yeah! Yeah! Yeah! Yeah!
 Ladies and gentlemen!
@@ -1862,17 +3478,105 @@
 We are FRUITS ZIPPER!</t>
         </is>
       </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="n">
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>Yeah! Yeah! Yeah! Yeah! Yeah! Yeah!
+Ladies and gentlemen!
+原宿 new kawaii スタイル
+It's showtime!
+Are you ready!
+We are the7人 ウワサの kawaii
+ところかまわず騒がします sorry!
+フロム 原宿 レペゼン カワラボ
+うちらが一番アゲちゃうってこと
+気づいてる?
+Yo! 端から端まで new kawaii!
+老若男女問わず new kawaii!
+言いたくなっちゃうよね new kawaii!
+さあさあ! もう一緒に new kawaii!
+ちぇけちぇけちぇけちぇけらーっ!
+なんでもいいからノッちゃいなーっ!
+音楽やっぱ楽しんだもん勝ちじゃん
+はい こっから歌パート
+この星に生まれた kawaii は
+どんなときも
+チカラになる
+今日も明日も明後日も
+信じ合える
+愛に変わるからーっ!
+Kawaii! Kawaii! Kawa! Kawa! Kawaii!
+Kawaii! Kawaii! Kawa! Kawa! Kawaii!
+Kawaii! Kawaii! Kawa! Kawa! Kawa! Kawa!
+We are FRUITS ZIPPER!
+Zipper! Zipper! ふるっぱーりー!
+New kawaii! デリバリー!
+朝まで! Shake your body!
+100人乗っても大丈夫っ!
+Zipper! Zipper! ふるっぱーりー!
+New kawaii! デリバリー!
+朝まで! Shake your body!
+100人乗っても大丈夫っ!
+Don't stop the party!
+ここがフィエスタ!
+騒げ! All day! All night!
+100人乗っても大丈夫っ!
+Non stop the music!
+ノリノリでダンシング!
+踊れ! エビバディーっ!
+101人目も乗っちゃってー!
+はじけるビート キラキラのハート
+夢を見せたいの 終わらないランド
+赤ちゃんからギャルピまでいんの
+7人7色で はい 全員集合っ!
+コールアンドレスポンス
+行くよー! Sayっ!
+あまねき! (あまねき!)
+おすず! (おすず!)
+ゆいちゃん! (ゆいちゃん!)
+るなぴ! (るなぴ!)
+まなふぃ! (まなふぃ!)
+まつかれ! (まつかれ!)
+ノエちゃん! (ノエちゃん!)
+We are FRUITS ZIPPER!
+この星で育った kawaii は
+どんなときも 勇気になる
+今日も明日も明後日も 繋ぎ合える
+愛に変わるからーっ!
+Kawaii! Kawaii! Kawa! Kawa! Kawaii!
+Kawaii! Kawaii! Kawa! Kawa! Kawaii!
+Kawaii! Kawaii! Kawa! Kawa! Kawa! Kawa!
+Are you ready!!
+We are FRUITS ZIPPER!
+Zipper! Zipper! ふるっぱーりー!
+New kawaii! デリバリー!
+朝まで! Shake your body!
+100人乗っても大丈夫っ!
+Zipper! Zipper! ふるっぱーりー!
+New kawaii! デリバリー!
+朝まで! Shake your body!
+100人乗っても大丈夫っ!
+Don't stop the party!
+ここがフィエスタ!
+騒げ! All day! All night!
+100人乗っても大丈夫っ!
+Non stop the music!
+ノリノリでダンシング!
+踊れ! エビバディーっ!
+101人目も乗っちゃってー!
+We are FRUITS ZIPPER!</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="409.5" customFormat="1" customHeight="1" s="2">
+      <c r="A31" s="2" t="n">
         <v>33</v>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B31" s="2" t="inlineStr">
         <is>
           <t>ふれふるサマー！</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="C31" s="2" t="inlineStr">
         <is>
           <t>君と過ごしたい夏が
 全速力　やってきた
@@ -1929,17 +3633,75 @@
 Ah...</t>
         </is>
       </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="n">
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>君と過ごしたい夏が
+全速力　やってきた
+誰にも負けない永遠の Stay Gold
+みんなみんな準備はどう？
+楽しんだもん勝ちじゃん
+アソビなんだ　本気でたたかえ
+熱くなれ　太陽よりもいちばん
+熱くなれ　輝いているのは誰だ？
+ひとなつっこいけどちょっと泣き虫
+原宿大好き　ダンスリーダー
+生まれも年も違うけど
+ステージにあがる瞬間　切り替えるスイッチ
+誰もが持ってるこのパワー　宇宙まで届け
+個性的なもぎたてのフレッシュなフルーツ
+熱い夏を虹色にするシャワービーナス
+大胆不敵なスプラッシュ
+振りまわせ　真夏の魅惑 Summer！！
+熱くなれ　太陽も溶ける Hot Dream
+声あげろ　この夏を楽しむ戦いは
+始まっているのだから　さぁ
+みんなでゆくのさ　ふれふるサマービーチ
+Ah　火照ったカラダ Summer Song
+あー　アイドル全開！極めるならやっぱりコレよね
+グループみんなを歌でひっぱる　それなら任せて
+誰よりポジティブでパリピ　楽しまなきゃでしょ
+この夏　いちばんの弾けそうなスタイルで
+誰よりも君の心を掴むんだ
+決戦の瞬間(とき)がキター！
+振りまわせ　空も飛べちゃうくらい
+熱くなれ　砂浜も焦がすほどに
+声あげろ　ひと夏の約束
+交わした
+ままで　今　君はどこにいるの？
+いっしょに最高の瞬間
+記憶に残そう
+この夏は　いつまでも終わらない
+この夏に　君が焼き付けるのは誰？
+声あげろ　永遠の始まり　それはそう
+きっとこの場所だから　さぁ
+みんなでゆくのさ　ふれふるサマービーチ
+Ah　火照ったカラダ Summer Song
+振りまわせ　真夏の魅惑 Summer！！
+熱くなれ　太陽も溶ける Hot Dream
+声あげろ　この夏を楽しむ戦いは
+始まっているのだから　さぁ
+みんなで飛ぶのさ　ふれふるサマービーチ
+Ah　火照ったカラダ　燃やそう(まだまだーー)
+フレーフレーフレッシュ
+この夏の主役に輝くのは
+フレーフレーフレッシュ
+他の誰でもないとしたらワタシ
+みんなでゆくのさ　ふれふるサマービーチ
+Ah　火照ったカラダ Summer Song
+Ah...</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="409.5" customFormat="1" customHeight="1" s="2">
+      <c r="A32" s="2" t="n">
         <v>35</v>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
         <is>
           <t>わたしの一番かわいいところ</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="C32" s="2" t="inlineStr">
         <is>
           <t>あれ気付いちゃいましたか？
 うまれて30秒。で最初に聞いた言葉は
@@ -2010,17 +3772,88 @@
 なんてありえない？</t>
         </is>
       </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="n">
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>あれ気付いちゃいましたか？
+うまれて30秒。で最初に聞いた言葉は
+当たり前にそりゃ覚えてないけど
+嬉しかったはず
+今でもだいたいのことは
+かわってないっていうかそりゃ
+中身は変わっていますので、その辺でも評価！(おねがい！)
+携帯のアンテナを光らせて
+それが超キュートなあの頃だって知ってたり。
+っていうかアンテナって何っていってるような
+わたしに
+付き合ってくれるの好き、
+逆にでもわたしのどこが好き？
+ねえ？ねえ？ねえ？
+わたしの一番、かわいいところに
+気付いてる
+そんな君が一番すごいすごいよすごすぎる！
+そして君が知ってるわたしが一番かわいいの、
+わたしもそれに気付いた！
+だから
+それかわいい、あれかわいいなんて
+誰かわいい、それかわいいなんて
+言わないで、わたし以外なんてやだ
+なんてありえない？
+わたし気付いちゃいました
+毎日何十秒、褒められまくったお菓子は
+他よりちょっと甘くなるって
+前に聞いたような
+さすがにそれなんか変だけど
+わたしは言われたいタイプでして
+もっとわかりやすくていいんだよ、お待ちしてます(おねがい！)
+何してもどんな顔見せてても
+いつも超キュートだって確信してるのは
+なんだかさ知らなかったタイプの運命の
+人なの？
+付き合ったりは無理ごめん
+逆にでもそれより楽しいよ
+ね！ね！ね！
+わたしの一番、かわいいところを
+よく見てる
+そんな君がほんとに超ラッキーな人すぎる！
+そして君が何年たってもそう思えるように
+わたしはそれに気付いた
+会えないときも、どんな表情してるかとか
+気持ちわるいくらい想像しちゃうから
+それかわいいあれかわいいよって
+ほんとにかわいいっていって
+わたしの一番、かわいいところに
+気付いてる
+そんな君が一番すごいすごいよすごすぎる！
+そして君が知ってるわたしが一番かわいいの、
+わたしもそれに気付いた！
+わたしの一番、かわいいところを
+よく見てる
+そんな君がほんとに超ラッキーな人すぎる！
+そして君が何年たってもそう思えるように
+わたしはそれに気付いた
+わたしの一番、かわいいところに
+気付いてる
+そんな君が一番すごいすごいよすごすぎる！
+そして君が知ってるわたしが一番かわいいの、
+わたしもそれに気付いた！
+だから
+それかわいい、あれかわいいなんて
+誰かわいい、それかわいいなんて
+言わないで、わたし以外なんてやだ
+なんてありえない？</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="409.5" customFormat="1" customHeight="1" s="2">
+      <c r="A33" s="2" t="n">
         <v>37</v>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B33" s="2" t="inlineStr">
         <is>
           <t>完璧主義で☆</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="C33" s="2" t="inlineStr">
         <is>
           <t>何度　バカと呼ばれたって
 もしもあざ笑われたって
@@ -2089,17 +3922,86 @@
 頑張るから…頑張るから、見ててっ？！？</t>
         </is>
       </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="n">
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>何度　バカと呼ばれたって
+もしもあざ笑われたって
+いつも　真っ直ぐでいられるのは…
+いつも　真っ直ぐでいられるのは…
+いつも　真っ直ぐでいられるのは…
+君が…
+ねぇ聞いてくれる？
+わたしの心の声を
+(Hey！ Hey！ Sing a Song！！！)
+寄り道なんかしたくないんですっ
+ねぇ聞かせてね？
+あなたの心の声を
+(Hey！ Hey！ Sing a Song！！！)
+高いフェンスは、LOVEでぶち抜けっ！
+竹下通りには、そう 1,2,3,4,5
+KAWAIIモノが
+誘惑してくるけど 1,2,3,4,5
+走り抜けたい、ナ
+何度　バカと呼ばれたって
+もしもあざ笑われたって
+気にせず歌い続けてみるよ
+完璧主義で☆
+大丈夫！(ほら)　大丈夫！(ほら)
+大丈夫！(ほら)　大丈夫だよ！
+信じてついて来てねっ！？
+何度もバカと呼ばれたって
+もしもあざ笑われたって
+いつも　真っ直ぐでいられるのは
+君がいるから
+明日も(その)　明日も(その)
+明日も(その)　明日もずっと
+頑張るから…頑張るから、見ててっ？！？
+ねぇ　知ってるかな？
+こんなに愛してること
+(Hey！ Hey！ Sing a Song！！！)
+大好きなんて越えちゃってます
+ねぇ　知ってるかな？
+キツい夜どうしてるか
+(Hey！ Hey！ Sing a Song！！！)
+君を想ってオヤスミしてます
+原宿を抜けたなら 1,2,3,4,5
+次のゴールは
+世界に飛んでいきたいの 1,2,3,4,5
+休むヒマはない、ナ
+何度　バカと呼ばれたって
+もしもあざ笑われたって
+気にせず歌い続けてみるよ
+完璧主義で☆
+明日も(その)　明日も(その)
+明日も(その)　明日もずっと
+すぐ側に…すぐ側に、居てねっ？！
+何度　バカと呼ばれたって
+もしもあざ笑われたって
+気にせず歌い続けてみるよ
+完璧主義で☆
+大丈夫！(ほら)　大丈夫！(ほら)
+大丈夫！(ほら)　大丈夫だよ！
+信じてついて来てねっ！？
+何度もバカと呼ばれたって
+もしもあざ笑われたって
+いつも　真っ直ぐでいられるのは
+君がいるから
+明日も(その)　明日も(その)
+明日も(その)　明日もずっと
+頑張るから…頑張るから、見ててっ？！？</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="409.5" customFormat="1" customHeight="1" s="2">
+      <c r="A34" s="2" t="n">
         <v>38</v>
       </c>
-      <c r="B34" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
         <is>
           <t>君と目があったとき</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="C34" s="2" t="inlineStr">
         <is>
           <t>(いくぞ)　(fu)
 君に出会ってからだよね？
@@ -2157,17 +4059,75 @@
 君とわたしならfufufu</t>
         </is>
       </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="n">
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>(いくぞ)(fu)
+君に出会ってからだよね？
+素顔の自分も好きになれそう
+君に出会ってからだよね？
+頭もなんか良くなった気がする
+君に出会ってからだよね
+ずっと先まで見通せそうな
+君に出会ってからだよね？
+とにかく色々良い感じ
+最高の魔法って意外と軽い
+そう気づいた
+とりあえず、出かける前に
+かけてみたらいいよ、そのマジック、つまり
+君がいるだけ、それだけで素敵
+見せて？
+君と目が、
+ねぇなんだか合ったとき
+わたしに夢がね、できました。きいてくれる？
+それはただ
+ねぇ結局そう君が、
+大きな夢叶えるとき、一緒にいたい
+そういうことです
+あとちょっといけそうだぞfu fu fu
+もうちょっと届きそうfu fu fu
+ふたつでひとつなのfufufu
+君とわたしならfufufu
+君に出会ってからだよね
+海の向こうまで目指せそうな
+君に出会ってからだよね？
+とにかくすべてがいい感じ
+最高のスタートって割とその時は
+そう気づかない
+とりあえず、始めてるから
+かけてみたらいいよ、そのチャンス、つまり
+君を信じる、それだけで奇跡
+君と目が
+ねぇなんだか合ったとき
+わたしに夢がね、できました。きいてくれる？
+君と手が
+ねぇなんだかふれたこと、
+小さな夢の始まりに、触ったみたい
+そういうことです
+見せて？
+君と目が、
+ねぇなんだか合ったとき
+わたしに夢がね、できました。きいてくれる？
+それはただ
+ねぇ結局そう君が、
+大きな夢叶えるとき、一緒にいたい
+そういうことです
+あとちょっといけそうだぞfu fu fu
+もうちょっと届きそうfu fu fu
+ふたつでひとつなのfufufu
+君とわたしならfufufu</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="409.5" customFormat="1" customHeight="1" s="2">
+      <c r="A35" s="2" t="n">
         <v>39</v>
       </c>
-      <c r="B35" t="inlineStr">
+      <c r="B35" s="2" t="inlineStr">
         <is>
           <t>君の明るい未来を追いかけて</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
+      <c r="C35" s="2" t="inlineStr">
         <is>
           <t>爽やかな朝日　まだ静かな街
 どんなドラマ待ってるのか　ワクワクで開くドア
@@ -2224,17 +4184,74 @@
 地図にない場所へ</t>
         </is>
       </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="n">
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>爽やかな朝日　まだ静かな街
+どんなドラマ待ってるのか　ワクワクで開くドア
+運命とか偶然　信じてないけど
+今日はなんだか　特別になる予感がする
+Say！ Hello Hello Hello
+小さな幸せを集めよう
+僕らのHello Hello Hello
+輝くよ
+巡り合って　語り合って
+素敵な夢がはじまる
+メロディーとリズムが重なり合う
+誰にだって　言えなかった
+愛と情熱の LIBERTY FORCE
+みんなで行こう　地図にない場所へ
+きっとここから
+わかりあえなくて　すれ違うときも
+いいとこどりして進もう
+もっと明るい明日へ
+たとえば奇跡を待っているよりも
+笑顔で探すそっちのほうが楽しいでしょ
+Say！ Hello Hello Hello
+集めた幸せを咲かせよう
+僕らのHello Hello Hello
+満開に
+見つめあって　ただ黙って
+流れる時間も好きだ
+思い出を1枚ずつ増やそう
+認めあって　伝えあった
+愛と友情のLIBERTY FORCE
+小さな一歩を合わせてはばたけ
+書きかけだった僕独りの物語に
+続きをくれたのは君だったんだ
+どんなドキドキだとか
+ハラハラかもね
+君と僕なら
+無敵だ
+だよね？
+誰にだって　隠したって
+隠しきれない愛がある
+言葉でさ　ちゃんと伝えていくよ
+君にだって　僕にだって
+それぞれひとつのLIBERTY FORCE
+どこでも行ける　自由を信じて
+巡り合って　混ざり合って
+素敵な夢をはじめよう
+メロディーとリズムで織り成すステージ
+誰にだって言えなかった
+愛と情熱の LIBERTY FORCE
+みんなで行こう　もっと遠くまで
+聞こえるでしょ？ Hello Hello Hello
+新しい世界の始まり
+僕らのHello Hello Hello
+地図にない場所へ</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="409.5" customFormat="1" customHeight="1" s="2">
+      <c r="A36" s="2" t="n">
         <v>41</v>
       </c>
-      <c r="B36" t="inlineStr">
+      <c r="B36" s="2" t="inlineStr">
         <is>
           <t>好き、お願い</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
+      <c r="C36" s="2" t="inlineStr">
         <is>
           <t>(I wish lovely line baby)
 (I wish lovely kiss baby)
@@ -2291,17 +4308,74 @@
 (I wish lovely line baby)</t>
         </is>
       </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="n">
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>(I wish lovely line baby)
+(I wish lovely kiss baby)
+(I wish lovely line baby)
+毎晩、眠る前、長すぎる妄想のストーリーは続く
+もしかしてどこからか本当になったりしない？
+いつの間にか寝ちゃってても定番のあれじゃ目覚めない
+ねえ大事なことは現実にとっておきたいの
+わたし、ドラマみたいな恋愛くらいしかしたくないです
+いざとなったら台本はないけど
+今、君に会えたここは第何話なんだろう？
+(dreamy dreamy love)
+長い長い夢みたいな
+恋はまだ初回のエンドロール
+もう少し顔を見ていたい
+キスには、お願い、ちょっとはやい
+遠い遠い夢だけは
+いつまでも憧れでいたい
+でもわたしがわたしの理想になれた日は
+そっと「好き」お願い
+今日も帰る前、イメージ通り「一緒に」って言ってくれない
+もしかしてちょっとだけこっちみたのがその合図？
+わかりにくい、そういうのもいい、大事に育てる感じ
+わざと一本遅い電車を待ってくれてたり
+少女漫画みたいな展開くらいしか知らないんです
+未完の名作ばっかりだけど
+今、君と話せたのは急展開すぎて
+(dreamy dreamy love)
+長い長い夢みたいな
+恋はまだ二回目のプロローグ
+もう少し様子見ていたい
+キスには、多分ね、ちょっとはやい
+遠い遠い夢だけは
+いつまでもそのままでいたい
+でもわたしが君の普通になれたとき
+きっと、好きになる
+星占いを信じたら
+土曜は運命の人に会う
+ってことは週末も君に会える、そういうこと？
+それでいいの、それがいいの
+夢じゃなくなったら
+幸せになれるかな
+まだこたえは出さなくていい恋を
+長い長い夢みたいな
+恋はまだ初回のエンドロール
+もう少し顔を見ていたい
+キスには、お願い、ちょっとはやい
+遠い遠い夢だけは
+いつまでも憧れでいたい
+でもわたしがわたしの理想になれた日は
+そっと「好き」お願い
+(I wish lovely line baby)
+(I wish lovely kiss baby)
+(I wish lovely line baby)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="409.5" customFormat="1" customHeight="1" s="2">
+      <c r="A37" s="2" t="n">
         <v>42</v>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="B37" s="2" t="inlineStr">
         <is>
           <t>世界はキミからはじまる</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
+      <c r="C37" s="2" t="inlineStr">
         <is>
           <t>世界が始まる予感　時が止まるような　ドキドキ　感情波打った
 今から　今から　今から　届けるよ　You are my treasure
@@ -2339,17 +4413,55 @@
 もっとずっと　描き続けるよ　嘘じゃない　瞬間　輝いた</t>
         </is>
       </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="n">
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>世界が始まる予感　時が止まるような　ドキドキ　感情波打った
+今から　今から　今から　届けるよ　You are my treasure
+伝えたい気持ちが　溢れた心を泳いで
+声にならない　吐き出せない　不器用すぎて嫌になる
+どうにもこうにも　ならない日々に
+向き合うこと教えてくれた見上げた　空は青く光る
+どこまでも果てしなく
+世界が始まる予感　トキメキを運んだ
+きっと後には戻れないような
+それでも　それでも　それでも　届けるよ　You are my treasure
+Ah　この両手に　抱えきれないくらいの想いを
+モノクロ物語だった　色をつけてくれたのはキミさ
+もっとずっと　描き続けるよ嘘じゃない
+瞬間　輝いた
+伝えようとしても　グルグル回り続けては
+言い訳を考えてる　きっかけの音を鳴らして
+どうせこのままじゃ　何も変わらない
+口癖　挫けそうになっても光を辿れば　キミだった
+いつだって　側にいてくれた
+世界が始まる予感　トキメキを運んだ　きっと後には戻れないような
+それでも　それでも　それでも　届けるよ　You are my treasure
+Ah　この両手に　抱えきれないくらいの想いを
+モノクロ　物語だった　色をつけてくれたのはキミさ
+もっとずっと　描き続けるよ嘘じゃない　瞬間　輝いた
+今ここにいる意味を　ここから見える景色も全部
+重ねたらキミが映った　ありがとうと愛してるを　伝えたくて
+ここから　これから先も
+ずっと一緒だって　忘れられないよう刻むんだ
+何度も　何度も　何度も　何度も何度だって伝えるよ
+世界はこんなにも美しかったんだ　巡り巡る季節感じて
+このまま　このまま　このまま　夢を見よう　You are my treasure
+Ah　この両手に抱えきれないくらいの想いを
+モノクロ　物語だった　色をつけてくれたのはキミさ
+もっとずっと　描き続けるよ嘘じゃない　瞬間　輝いた</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="409.5" customFormat="1" customHeight="1" s="2">
+      <c r="A38" s="2" t="n">
         <v>43</v>
       </c>
-      <c r="B38" t="inlineStr">
+      <c r="B38" s="2" t="inlineStr">
         <is>
           <t>成長期なので。</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
+      <c r="C38" s="2" t="inlineStr">
         <is>
           <t>なんでも、かんでも、全部を、
 完璧、ちょっぴり丁寧にこなすって
@@ -2411,17 +4523,79 @@
 だってわたし達、成長期なので。</t>
         </is>
       </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="n">
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>なんでも、かんでも、全部を、
+完璧、ちょっぴり丁寧にこなすって
+難しいって誰かは言うけれど
+(できる、できる！わたし、できる！)
+大事な　大事な　大事な　大事な
+大事なきみに出会えたんです
+嬉しいんです
+だから、やるしかないの！
+(できる、できる！みんなで、できる！)
+不器用だって
+ねむむだって
+未完成だって
+(ノビシロ見せつけるもん！)
+1日が204時間にならんかな？？
+ほしいモノはただ一つ　でも、
+ひ　み　つ
+今日も貪欲なんです
+コレわたし達でーす
+まだまだだ　バタバタタ
+頑張るるのだだ
+君の夢とわたしの夢が同じだって知った日から
+(世界がSHINYです！)
+きみが居れば叶えられる気がする
+だってわたし達、成長期なので。
+なんでも、かんでも、大好き、
+ギュッてし、天使の対応無理かもって
+そりゃそうです。こちとら人間なので。
+(しゃーない、しゃーない！
+しゃーない、しゃーないよ！)
+だけど大事な大事な大事な仲間たちには
+ドドカンとめちゃドカンと
+正面から向き合うの
+(話し合いはゼッタイ！)
+道に迷っちゃうのは週8だけど
+早起きしてダッシュするから大丈夫！
+エナジー溜めるし、大丈夫！
+かなり貪欲なんです
+ちょっとワガママでーす
+アレもしたい！コレもしたい！
+全部したいのだだ
+涙出るくらい応援してくれる君を守らせて
+(一緒にReady Go！)
+その笑顔しかいらない気がしちゃう
+だってわたし達、成長期なので。
+君と見たい景色も
+君としたい話も
+"君"を知りたいわたしも
+君に教えたい"わたし"も
+まだまだまだまだまだまだ…
+今日も貪欲なんです
+コレわたし達でーす
+まだまだだ　バタバタタ
+頑張るるのだだ
+君の夢とわたしの夢が同じだって知った日から
+(一緒にReady Go！)
+きみが居れば叶えられる気がする
+たまにわたし達、成長痛です。
+だってわたし達、成長期なので。</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="409.5" customFormat="1" customHeight="1" s="2">
+      <c r="A39" s="2" t="n">
         <v>44</v>
       </c>
-      <c r="B39" t="inlineStr">
+      <c r="B39" s="2" t="inlineStr">
         <is>
           <t>超めでたいソング〜こんなに幸せでいいのかな？〜</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
+      <c r="C39" s="2" t="inlineStr">
         <is>
           <t>(oh　めでたい)
 (おめでたい)
@@ -2487,17 +4661,83 @@
 最高の今に、おめでとうだよ！</t>
         </is>
       </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="n">
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>(oh　めでたい)
+(おめでたい)
+(超めでたい)
+(小めでたい？)
+(中めでたい？)
+(大めでたい？)
+本日、ハレの日、雨でも晴れ
+一生に一度のエブリデイだけど
+やっぱり今日はスペシャル
+本日の衣装は悩みません
+一周まわってまあシンプルだけど
+あれでもやっぱ派手すぎ？
+来年の今は記念日
+それまではたくさんもっと
+どうでもいいことと、貯金とかもしよう
+(そして大事なこと)
+まずはトゥデイをブチ上げよ？
+(おめでとう！)
+わたし
+こんなに幸せでいいのかな？(いいのかな？)
+なんて本当はそんなこと悩んでないけど
+だって、ちょっとくらいのマイナスもなきゃ
+って思うくらいにいい感じ(なんです！)
+まあねこんなに幸せでいいのです(いいのです)
+だってわたし自分で選んだんだから
+いぬはかけまわり、ねこはかわいいし
+青い鳥は飛ぶ、
+みんながいる！
+当日はケの日、普通に良い
+一生で一番、ヤングな日だけど
+仕方ないです
+って感じで冷めたりもしてるよ
+サプライズのメッセージ
+驚くはずないってお決まり
+一昨年の今は他人で
+これまではたくさんもっと
+無駄かもってことと、恋愛とかしたね
+(だけど大事なこと)
+今はほんとに大好きです
+(おめでとう！)
+あなた
+こんなに幸せでいいのかな？(いいのかな？)
+なんて本当はそんなこと心配ないけど
+だって、ちょっとくらいの試練とかもなきゃ
+って思うくらいのいい感じ(なんです！)
+まあね結局幸せでいいのです(いいのです)
+だってわたしちゃんと戦ったんだから
+おみこしにのって、花火もあげて
+いいことはぜんぶ
+一度にしよう！
+(おめでとう！)
+わたし
+こんなに幸せでいいのかな？(いいのかな？)
+なんて本当はそんなこと悩んでないけど
+だって、ちょっとくらいのマイナスもなきゃ
+って思うくらいにいい感じ(なんです！)
+まあねこんなに幸せでいいのです(いいのです)
+だってわたし自分で選んだんだから
+いぬはかけまわり、ねこはかわいいし
+青い鳥は飛ぶ、
+みんながいる！
+最高の今に、おめでとうだよ！</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="409.5" customFormat="1" customHeight="1" s="2">
+      <c r="A40" s="2" t="n">
         <v>49</v>
       </c>
-      <c r="B40" t="inlineStr">
+      <c r="B40" s="2" t="inlineStr">
         <is>
           <t>ふるっぱれーど</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
+      <c r="C40" s="2" t="inlineStr">
         <is>
           <t>いっせーの
 はじまりの合図
@@ -2572,17 +4812,92 @@
 (いちにさんしごー！)</t>
         </is>
       </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="n">
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>いっせーの
+はじまりの合図
+全体、前にならえ！
+OK！
+それじゃはしゃごう
+Let's go FRUITS ZIPPER
+papa-n papa-n
+(いちにさんしごー！)
+papa-n papa-n
+(いちにさん)
+(いぇい！)
+なんとなく超いい感じ
+おしゃれをしたりちょっぴりドキドキ
+前髪は拘りの見せ所だし(いのち笑)
+誰よりも自分愛していこう
+自由でいたいもん
+ラブで世界を廻そう
+(はい　せーの！)
+カラフルっパレード
+ボクらはみな何かに恋してる
+きゅんときゅんが出会い
+止まれないでしょ！進め！
+がんばれ！
+信じることでココロを抱きしめて
+ぎゅってしたら大丈夫だよ　ほら　ね
+ワンツーあふれる感情
+ワンチャン！で飛び出し渋滞
+やっちゃった完全に後悔
+あたまがとけちゃうの
+ノーノーノー
+暗い暗い地球の果てで
+ボクらは手探り繰り返すよ
+目の前のリアルさえも見失ってしまわぬように
+精一杯走り続けるよ
+YO　シャッター越しじゃわかんない心裏
+よくみてみてよあっという間に
+今日が昨日に明日が昨日に
+明後日も明明後日も
+ただ過去に
+あの時の思いもひとりきりで抱えないで
+一緒に行こう
+ねぇ約束だよ
+誰よりも自分愛していこう
+自由でいたいもん
+ラブで世界を廻そう
+(はい　せーの！)
+カラフルっパレード
+あのコもみな何かに恋してる
+ピカピカの時代
+飾りたいでしょ！進め！
+胸張れっ！
+声を上げてさあ大好きを届け合おう
+ぐっときたら感動しちゃうかもね
+ワンツーあふれる感情
+ワンチャン！で超えちゃう限界
+やっぱね完全に正解
+未来は明るいの
+カラフルっパレード
+ボクらはみな何かに恋してる
+きゅんときゅんが出会い
+止まれないでしょ！進め！
+がんばれ！
+信じることでココロを抱きしめて
+最高の輝きをもういっちょ！
+ほい！
+最強の味方だよ
+Weare FRUITS ZIPPER！！
+papa-n papa-n
+(いちにさんしごー！)
+papa-n papa-n
+(いちにさんしごー！)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="409.5" customFormat="1" customHeight="1" s="2">
+      <c r="A41" s="2" t="n">
         <v>507</v>
       </c>
-      <c r="B41" t="inlineStr">
+      <c r="B41" s="2" t="inlineStr">
         <is>
           <t>ぱわーオブらぶ</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
+      <c r="C41" s="2" t="inlineStr">
         <is>
           <t>ぱぱわわ、ぱぱわぱぱ、
 ぱぱわわ、ぱぱわぱぱ、ぱぱわわ、ぱぱわぱぱ、ぱ
@@ -2596,13 +4911,9 @@
 左手にそれ
 あわせてらぶ
 そのパワーです
-ぱぱわわ、ぱぱわぱぱ、
-ぱぱわわ、ぱぱわぱぱ、ぱぱわわ、ぱぱわぱぱ、ぱ
 (わたしを見て君が元気になって、
 その君を見たわたしがまた元気になる
 パワーの循環、永久機関、そんなパワー)
-ぱぱわわ、ぱぱわぱぱ、
-ぱぱわわ、ぱぱわぱぱ、ぱぱわわ、ぱぱわぱぱ、ぱ
 (パワーがあればなんでもできるから
 さらにもうちょっとパワーを増やして
 もっとなんでもできるってパワー)
@@ -2632,12 +4943,8 @@
 左手は君
 あわせてらぶ
 みんなでらぶ
-ぱぱわわ、ぱぱわぱぱ、
-ぱぱわわ、ぱぱわぱぱ、ぱぱわわ、ぱぱわぱぱ、ぱ
 (強い力とか弱い力とか重力とか電磁気力とか、
 パワー界隈も色々あります、結局ぜんぶがパワー)
-ぱぱわわ、ぱぱわぱぱ、
-ぱぱわわ、ぱぱわぱぱ、ぱぱわわ、ぱぱわぱぱ、ぱ
 (自分を愛してあげなきゃ
 誰かを愛するパワーも生まれないって、
 大切なことを続ける言葉のパワー)
@@ -2666,17 +4973,93 @@
 ぜんぶあわせてフルパワー</t>
         </is>
       </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="n">
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>ぱぱわわ、ぱぱわぱぱ、
+ぱぱわわ、ぱぱわぱぱ、ぱぱわわ、ぱぱわぱぱ、ぱ
+ぱぱわわ、ぱぱわぱぱ、
+ぱぱわわ、ぱぱわぱぱ、ぱぱわわ、ぱぱわぱぱ、ぱ
+右手に「ぱ」
+左手に「わ」
+あわせてパワー
+フルパワーです
+右手にこれ
+左手にそれ
+あわせてらぶ
+そのパワーです
+(わたしを見て君が元気になって、
+その君を見たわたしがまた元気になる
+パワーの循環、永久機関、そんなパワー)
+(パワーがあればなんでもできるから
+さらにもうちょっとパワーを増やして
+もっとなんでもできるってパワー)
+心ちょっとだけ充電まっててね
+つまり愛をためて、好きをためて、
+からだちょっとだけ充電まっててね
+そしてたまりたまります、これ
+世界中の笑顔ここにあつめてWER
+エブリbody body に愛と夢をチャージします
+宇宙中のパワーここにあつめてPA
+地球飛び出すくらいに気持ちを叫ぼうよ
+oh yeah
+わたしのパワーあなたのパワー
+だれかのパワーみんなのパワー
+パパパワー、ママパワー、
+おじいちゃんおばあちゃんパワー、
+好きな人パワー
+ごはんのパワー、おやつのパワー
+おふろのパワー、すいみんパワー
+このパワー、そのパワー、
+ぜんぶあわせてフルパワー
+まるとって「は」
+そのままで「わ」
+あわせて「はわ？」
+ゼロパワーです？
+右手わたし
+左手は君
+あわせてらぶ
+みんなでらぶ
+(強い力とか弱い力とか重力とか電磁気力とか、
+パワー界隈も色々あります、結局ぜんぶがパワー)
+(自分を愛してあげなきゃ
+誰かを愛するパワーも生まれないって、
+大切なことを続ける言葉のパワー)
+世界中、輝く光あつめてWER
+エブリbody body とその未来を照らしちゃいます
+宇宙中、轟く存在(ひと)になってふるっぱー
+地球飛び出すくらいにこの歌、歌おうよ
+oh yeah
+たまにちょっとだけお手を拝借で
+つまり手をつないだりもしたい
+あとはちょっとだけ見つめ合ったりね
+そしてわかる？わかります、よね
+世界中の笑顔ここにあつめてWER
+エブリbody body に愛と夢をチャージします
+宇宙中のパワーここにあつめてPA
+地球飛び出すくらいに気持ちを叫ぼうよ
+oh yeah
+わたしのパワー、あなたのパワー
+だれかのパワー、みんなのパワー
+パパパワー、ママパワー、
+おじいちゃんおばあちゃんパワー、
+好きな人パワー
+ごはんのパワー、おやつのパワー
+おふろのパワー、すいみんパワー
+このパワー、そのパワー、
+ぜんぶあわせてフルパワー</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="409.5" customFormat="1" customHeight="1" s="2">
+      <c r="A42" s="2" t="n">
         <v>508</v>
       </c>
-      <c r="B42" t="inlineStr">
+      <c r="B42" s="2" t="inlineStr">
         <is>
           <t>センセーション</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
+      <c r="C42" s="2" t="inlineStr">
         <is>
           <t>はぁ、こんがらがって
 混沌　混濁の世界じゃ
@@ -2736,6 +5119,66 @@
 ねぇ、アソぼ？</t>
         </is>
       </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>はぁ、こんがらがって
+混沌　混濁の世界じゃ
+もう、やってられないし
+見えない　聞こえない
+そう、グーチョキパーの
+ジャンケンでも負ける気しないわ
+気持ちでは負けないし　切り取るの
+こう見えたって　心の中
+ガラス製なの
+見えない？　見えない？
+ワレモノ注意　切り込み中尉
+なんでもかんでも期待しないでよ
+アイヘイチュー　ヘイチュー
+凄惨な街の現状　計算外　むしろ平常？
+ノイズだらけこの世界
+もしもあっちもこっちも巻き起こせるなら
+まるで絶唱　狂騒　センセーション
+わたし　なんでもかんでもお見通しなの
+そう有能
+カッティン　カッティン　切り裂いて
+ねぇ、アソぼ？
+あぁ、彷徨ったって
+巻き戻りゃしないわ
+もう、やってられないし
+癒えない　癒えない
+そんじょそこらの
+奴らと一緒にしないで
+わたしの中じゃ1番なの
+そうは言っても　本当のとこ
+誰も彼も
+知らない　知らない
+ハレモノだって　バケモノだって
+あいつもこいつも酷い仕打ちよね
+アイヘイチュー　ヘイチュー
+体裁だけ気にしちゃって
+平静だけは装って
+一寸先闇の世界　アイ　アイ
+もしもにっちもさっちも行かない時はね
+ありゃま、絶唱　残響　センセーション
+わたし　なんでもかんでもお見通しなの
+So,　you　know？
+カッティン カッティン 切り裂いて
+刻むだけ Ah
+凄惨な街の現状　計算外　むしろ平常？
+ノイズだらけこの世界
+もしもあっちもこっちも巻き起こせるなら
+まるで絶唱　狂騒　センセーション
+わたし　なんでもかんでもお見通しなの
+そう有能カッティン　カッティン
+アソびましょ
+もしもあっちもこっちも巻き起こせるなら
+まるで絶唱　狂騒　センセーション
+わたし　なんでもかんでもお見通しなの
+そう言うの
+カッティン　カッティン　切り裂いて
+ねぇ、アソぼ？</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2748,8 +5191,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1914"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:I1914"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
@@ -2757,6 +5200,7 @@
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="8" customWidth="1" min="5" max="5"/>
     <col width="80" customWidth="1" min="6" max="6"/>
+    <col width="60" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2790,6 +5234,17 @@
           <t>lyric</t>
         </is>
       </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>lyric_col</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>col_space</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="n"/>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -3111,6 +5566,9 @@
 猫かぶって</t>
         </is>
       </c>
+      <c r="G13" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -3137,6 +5595,9 @@
           <t>合わせて笑うの疲れちゃった</t>
         </is>
       </c>
+      <c r="G14" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -3350,6 +5811,14 @@
           <t>今が</t>
         </is>
       </c>
+      <c r="G22" t="n">
+        <v>1</v>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>half</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3376,6 +5845,14 @@
           <t>ここが</t>
         </is>
       </c>
+      <c r="G23" t="n">
+        <v>2</v>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>half</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3402,6 +5879,14 @@
           <t>彼が</t>
         </is>
       </c>
+      <c r="G24" t="n">
+        <v>3</v>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>half</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3428,6 +5913,14 @@
           <t>雨の</t>
         </is>
       </c>
+      <c r="G25" t="n">
+        <v>4</v>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>half</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3454,6 +5947,9 @@
           <t>夜が</t>
         </is>
       </c>
+      <c r="G26" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -5226,6 +7722,14 @@
           <t>最強メンタリティ</t>
         </is>
       </c>
+      <c r="G93" t="n">
+        <v>1</v>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>half</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -5252,6 +7756,9 @@
           <t>この現在地</t>
         </is>
       </c>
+      <c r="G94" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -5278,6 +7785,14 @@
           <t>押すだけじゃないの？</t>
         </is>
       </c>
+      <c r="G95" t="n">
+        <v>1</v>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>half</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -5304,6 +7819,9 @@
           <t>Enterキー</t>
         </is>
       </c>
+      <c r="G96" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -5330,6 +7848,14 @@
           <t>本音チラつかす</t>
         </is>
       </c>
+      <c r="G97" t="n">
+        <v>1</v>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>half</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -5356,6 +7882,9 @@
           <t>Zip up！ Zip down！</t>
         </is>
       </c>
+      <c r="G98" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -5382,6 +7911,9 @@
           <t>何度だって</t>
         </is>
       </c>
+      <c r="G99" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -5408,6 +7940,9 @@
           <t>失敗したい</t>
         </is>
       </c>
+      <c r="G100" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -5486,6 +8021,14 @@
           <t>このドキドキは何でしょう？</t>
         </is>
       </c>
+      <c r="G103" t="n">
+        <v>1</v>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>half</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -5512,6 +8055,9 @@
           <t>恋の万華鏡？</t>
         </is>
       </c>
+      <c r="G104" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -5642,6 +8188,9 @@
           <t>飛び出し注意　なんて無視して</t>
         </is>
       </c>
+      <c r="G109" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -5668,6 +8217,9 @@
           <t>「今夜こそ！」</t>
         </is>
       </c>
+      <c r="G110" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -6220,6 +8772,9 @@
           <t>ウザいくらいの</t>
         </is>
       </c>
+      <c r="G131" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -6246,6 +8801,9 @@
           <t>カンフル剤</t>
         </is>
       </c>
+      <c r="G132" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -6272,6 +8830,9 @@
           <t>個性とコスメの</t>
         </is>
       </c>
+      <c r="G133" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -6298,6 +8859,9 @@
           <t>ギャングスタ</t>
         </is>
       </c>
+      <c r="G134" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -6324,6 +8888,9 @@
           <t>自尊ヴァイヴス</t>
         </is>
       </c>
+      <c r="G135" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -6350,6 +8917,9 @@
           <t>激アゲ中な</t>
         </is>
       </c>
+      <c r="G136" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -6376,6 +8946,14 @@
           <t>負ける気がせん！</t>
         </is>
       </c>
+      <c r="G137" t="n">
+        <v>1</v>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>half</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -6402,6 +8980,9 @@
           <t>なんちゅーか！</t>
         </is>
       </c>
+      <c r="G138" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -6454,6 +9035,9 @@
           <t>ブラジル・ニューヨーク・バンクーバー</t>
         </is>
       </c>
+      <c r="G140" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -6480,6 +9064,14 @@
           <t>満腹中枢バグったLove</t>
         </is>
       </c>
+      <c r="G141" t="n">
+        <v>1</v>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>half</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -6506,6 +9098,9 @@
           <t>地球ZipしてTaxiったら</t>
         </is>
       </c>
+      <c r="G142" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -6610,6 +9205,9 @@
           <t>時は金なり　まだ見ぬ世界で</t>
         </is>
       </c>
+      <c r="G146" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -6636,6 +9234,9 @@
           <t>今夜だけ！</t>
         </is>
       </c>
+      <c r="G147" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -7136,6 +9737,14 @@
 愛はバルクだ</t>
         </is>
       </c>
+      <c r="G166" t="n">
+        <v>1</v>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>half</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -7162,6 +9771,9 @@
           <t>Pump Up Pump Up Pump Up</t>
         </is>
       </c>
+      <c r="G167" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -10005,6 +12617,14 @@
           <t>wow wow wow wow wow wow</t>
         </is>
       </c>
+      <c r="G275" t="n">
+        <v>1</v>
+      </c>
+      <c r="H275" t="inlineStr">
+        <is>
+          <t>break</t>
+        </is>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="n">
@@ -10031,6 +12651,9 @@
           <t>新しい！</t>
         </is>
       </c>
+      <c r="G276" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="n">
@@ -10057,6 +12680,14 @@
           <t>パンダ的な雰囲気もいいよね</t>
         </is>
       </c>
+      <c r="G277" t="n">
+        <v>1</v>
+      </c>
+      <c r="H277" t="inlineStr">
+        <is>
+          <t>half</t>
+        </is>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="n">
@@ -10083,6 +12714,9 @@
           <t>（いいよね）</t>
         </is>
       </c>
+      <c r="G278" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="n">
@@ -10135,6 +12769,14 @@
           <t>お姫様な扱いもいいよね</t>
         </is>
       </c>
+      <c r="G280" t="n">
+        <v>1</v>
+      </c>
+      <c r="H280" t="inlineStr">
+        <is>
+          <t>half</t>
+        </is>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="n">
@@ -10161,6 +12803,9 @@
           <t>（もちろんいいよね）</t>
         </is>
       </c>
+      <c r="G281" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="n">
@@ -10450,6 +13095,14 @@
           <t>update、update</t>
         </is>
       </c>
+      <c r="G292" t="n">
+        <v>1</v>
+      </c>
+      <c r="H292" t="inlineStr">
+        <is>
+          <t>half</t>
+        </is>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="n">
@@ -10476,6 +13129,9 @@
           <t>したデートで</t>
         </is>
       </c>
+      <c r="G293" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="n">
@@ -10502,6 +13158,14 @@
           <t>oh oh oh oh oh oh</t>
         </is>
       </c>
+      <c r="G294" t="n">
+        <v>1</v>
+      </c>
+      <c r="H294" t="inlineStr">
+        <is>
+          <t>half</t>
+        </is>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="n">
@@ -10528,6 +13192,9 @@
           <t>全員参加で</t>
         </is>
       </c>
+      <c r="G295" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="296">
       <c r="A296" t="n">
@@ -10554,6 +13221,14 @@
           <t>a new world a new world</t>
         </is>
       </c>
+      <c r="G296" t="n">
+        <v>1</v>
+      </c>
+      <c r="H296" t="inlineStr">
+        <is>
+          <t>half</t>
+        </is>
+      </c>
     </row>
     <row r="297">
       <c r="A297" t="n">
@@ -10580,6 +13255,9 @@
           <t>そんなワードで</t>
         </is>
       </c>
+      <c r="G297" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="298">
       <c r="A298" t="n">
@@ -10684,6 +13362,14 @@
           <t>どっちでもない雰囲気もいいよね？</t>
         </is>
       </c>
+      <c r="G301" t="n">
+        <v>1</v>
+      </c>
+      <c r="H301" t="inlineStr">
+        <is>
+          <t>half</t>
+        </is>
+      </c>
     </row>
     <row r="302">
       <c r="A302" t="n">
@@ -10710,6 +13396,9 @@
           <t>（いいよね）</t>
         </is>
       </c>
+      <c r="G302" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="303">
       <c r="A303" t="n">
@@ -10762,6 +13451,14 @@
           <t>王子様は未定でもいいよね</t>
         </is>
       </c>
+      <c r="G304" t="n">
+        <v>1</v>
+      </c>
+      <c r="H304" t="inlineStr">
+        <is>
+          <t>half</t>
+        </is>
+      </c>
     </row>
     <row r="305">
       <c r="A305" t="n">
@@ -10788,6 +13485,9 @@
           <t>（もちろんいいよね）</t>
         </is>
       </c>
+      <c r="G305" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="306">
       <c r="A306" t="n">
@@ -11077,6 +13777,14 @@
           <t>update update</t>
         </is>
       </c>
+      <c r="G316" t="n">
+        <v>1</v>
+      </c>
+      <c r="H316" t="inlineStr">
+        <is>
+          <t>half</t>
+        </is>
+      </c>
     </row>
     <row r="317">
       <c r="A317" t="n">
@@ -11103,6 +13811,9 @@
           <t>したデートで</t>
         </is>
       </c>
+      <c r="G317" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="318">
       <c r="A318" t="n">
@@ -11129,6 +13840,14 @@
           <t>oh oh oh oh oh oh</t>
         </is>
       </c>
+      <c r="G318" t="n">
+        <v>1</v>
+      </c>
+      <c r="H318" t="inlineStr">
+        <is>
+          <t>half</t>
+        </is>
+      </c>
     </row>
     <row r="319">
       <c r="A319" t="n">
@@ -11155,6 +13874,9 @@
           <t>自由参加で</t>
         </is>
       </c>
+      <c r="G319" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="320">
       <c r="A320" t="n">
@@ -11181,6 +13903,14 @@
           <t>a new world a new world</t>
         </is>
       </c>
+      <c r="G320" t="n">
+        <v>1</v>
+      </c>
+      <c r="H320" t="inlineStr">
+        <is>
+          <t>half</t>
+        </is>
+      </c>
     </row>
     <row r="321">
       <c r="A321" t="n">
@@ -11207,6 +13937,9 @@
           <t>そんなワードで</t>
         </is>
       </c>
+      <c r="G321" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="322">
       <c r="A322" t="n">
@@ -11521,6 +14254,14 @@
           <t>update、update</t>
         </is>
       </c>
+      <c r="G333" t="n">
+        <v>1</v>
+      </c>
+      <c r="H333" t="inlineStr">
+        <is>
+          <t>half</t>
+        </is>
+      </c>
     </row>
     <row r="334">
       <c r="A334" t="n">
@@ -11547,6 +14288,9 @@
           <t>したデートで</t>
         </is>
       </c>
+      <c r="G334" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="335">
       <c r="A335" t="n">
@@ -11573,6 +14317,14 @@
           <t>oh oh oh oh oh oh</t>
         </is>
       </c>
+      <c r="G335" t="n">
+        <v>1</v>
+      </c>
+      <c r="H335" t="inlineStr">
+        <is>
+          <t>half</t>
+        </is>
+      </c>
     </row>
     <row r="336">
       <c r="A336" t="n">
@@ -11599,6 +14351,9 @@
           <t>全員参加で</t>
         </is>
       </c>
+      <c r="G336" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="337">
       <c r="A337" t="n">
@@ -11625,6 +14380,14 @@
           <t>a new world a new world</t>
         </is>
       </c>
+      <c r="G337" t="n">
+        <v>1</v>
+      </c>
+      <c r="H337" t="inlineStr">
+        <is>
+          <t>half</t>
+        </is>
+      </c>
     </row>
     <row r="338">
       <c r="A338" t="n">
@@ -11651,6 +14414,9 @@
           <t>そんなワードで</t>
         </is>
       </c>
+      <c r="G338" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="339">
       <c r="A339" t="n">
@@ -11755,6 +14521,9 @@
           <t>セカイに</t>
         </is>
       </c>
+      <c r="G342" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="343">
       <c r="A343" t="n">
@@ -11781,6 +14550,9 @@
           <t>走るセンセーション</t>
         </is>
       </c>
+      <c r="G343" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="344">
       <c r="A344" t="n">
@@ -11807,6 +14579,9 @@
           <t>満天の星ぎゅっと</t>
         </is>
       </c>
+      <c r="G344" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="345">
       <c r="A345" t="n">
@@ -11833,6 +14608,9 @@
           <t>抱きしめ</t>
         </is>
       </c>
+      <c r="G345" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="346">
       <c r="A346" t="n">
@@ -11859,6 +14637,9 @@
           <t>旅に出よう</t>
         </is>
       </c>
+      <c r="G346" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="347">
       <c r="A347" t="n">
@@ -11885,6 +14666,9 @@
           <t>全宇宙巻き込んで</t>
         </is>
       </c>
+      <c r="G347" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="348">
       <c r="A348" t="n">
@@ -11911,6 +14695,9 @@
           <t>いっちょ突破</t>
         </is>
       </c>
+      <c r="G348" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="349">
       <c r="A349" t="n">
@@ -12252,6 +15039,9 @@
           <t>カラフル</t>
         </is>
       </c>
+      <c r="G361" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="362">
       <c r="A362" t="n">
@@ -12278,6 +15068,9 @@
           <t>さながらファンタジー</t>
         </is>
       </c>
+      <c r="G362" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="363">
       <c r="A363" t="n">
@@ -12356,6 +15149,9 @@
           <t>脳に染みてく</t>
         </is>
       </c>
+      <c r="G365" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="366">
       <c r="A366" t="n">
@@ -12382,6 +15178,9 @@
           <t>好奇心のトキメキ</t>
         </is>
       </c>
+      <c r="G366" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="367">
       <c r="A367" t="n">
@@ -12408,6 +15207,14 @@
           <t>楽しいこと</t>
         </is>
       </c>
+      <c r="G367" t="n">
+        <v>1</v>
+      </c>
+      <c r="H367" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
     </row>
     <row r="368">
       <c r="A368" t="n">
@@ -12434,6 +15241,9 @@
           <t>一緒に感じたいの</t>
         </is>
       </c>
+      <c r="G368" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="369">
       <c r="A369" t="n">
@@ -12460,6 +15270,14 @@
           <t>こぼさないで</t>
         </is>
       </c>
+      <c r="G369" t="n">
+        <v>1</v>
+      </c>
+      <c r="H369" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
     </row>
     <row r="370">
       <c r="A370" t="n">
@@ -12486,6 +15304,9 @@
           <t>ちゃんと受け取ってさ！</t>
         </is>
       </c>
+      <c r="G370" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="371">
       <c r="A371" t="n">
@@ -12512,6 +15333,14 @@
           <t>アアア　チェック　ワンツー</t>
         </is>
       </c>
+      <c r="G371" t="n">
+        <v>1</v>
+      </c>
+      <c r="H371" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
     </row>
     <row r="372">
       <c r="A372" t="n">
@@ -12538,6 +15367,9 @@
           <t>で途切れる交信中？</t>
         </is>
       </c>
+      <c r="G372" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="373">
       <c r="A373" t="n">
@@ -12564,6 +15396,9 @@
           <t>ノッティスミー！</t>
         </is>
       </c>
+      <c r="G373" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="374">
       <c r="A374" t="n">
@@ -12590,6 +15425,9 @@
           <t>マッシュ！マッシュ！マッシュ！</t>
         </is>
       </c>
+      <c r="G374" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="375">
       <c r="A375" t="n">
@@ -12616,6 +15454,9 @@
           <t>スマッシュ</t>
         </is>
       </c>
+      <c r="G375" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="376">
       <c r="A376" t="n">
@@ -12642,6 +15483,9 @@
           <t>かませよー</t>
         </is>
       </c>
+      <c r="G376" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="377">
       <c r="A377" t="n">
@@ -12746,6 +15590,9 @@
           <t>繋がれ点と点</t>
         </is>
       </c>
+      <c r="G380" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="381">
       <c r="A381" t="n">
@@ -12772,6 +15619,9 @@
           <t>結んで線と線</t>
         </is>
       </c>
+      <c r="G381" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="382">
       <c r="A382" t="n">
@@ -12798,6 +15648,9 @@
           <t>この指</t>
         </is>
       </c>
+      <c r="G382" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="383">
       <c r="A383" t="n">
@@ -12824,6 +15677,14 @@
           <t>とまれ</t>
         </is>
       </c>
+      <c r="G383" t="n">
+        <v>2</v>
+      </c>
+      <c r="H383" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
     </row>
     <row r="384">
       <c r="A384" t="n">
@@ -12850,6 +15711,9 @@
           <t>でせーので返事！</t>
         </is>
       </c>
+      <c r="G384" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="385">
       <c r="A385" t="n">
@@ -12876,6 +15740,9 @@
           <t>はーい！！！</t>
         </is>
       </c>
+      <c r="G385" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="386">
       <c r="A386" t="n">
@@ -12928,6 +15795,9 @@
           <t>これが我らの煌煌の</t>
         </is>
       </c>
+      <c r="G387" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="388">
       <c r="A388" t="n">
@@ -12954,6 +15824,9 @@
           <t>ショータイム！</t>
         </is>
       </c>
+      <c r="G388" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="389">
       <c r="A389" t="n">
@@ -13006,6 +15879,9 @@
           <t>セカイが</t>
         </is>
       </c>
+      <c r="G390" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="391">
       <c r="A391" t="n">
@@ -13032,6 +15908,9 @@
           <t>ゆれるハイテンション</t>
         </is>
       </c>
+      <c r="G391" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="392">
       <c r="A392" t="n">
@@ -13058,6 +15937,9 @@
           <t>満天の星ずっと</t>
         </is>
       </c>
+      <c r="G392" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="393">
       <c r="A393" t="n">
@@ -13084,6 +15966,9 @@
           <t>照らすよ</t>
         </is>
       </c>
+      <c r="G393" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="394">
       <c r="A394" t="n">
@@ -13110,6 +15995,9 @@
           <t>どこまでも</t>
         </is>
       </c>
+      <c r="G394" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="395">
       <c r="A395" t="n">
@@ -13136,6 +16024,9 @@
           <t>全宇宙巻き込んで</t>
         </is>
       </c>
+      <c r="G395" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="396">
       <c r="A396" t="n">
@@ -13162,6 +16053,9 @@
           <t>いっせーので</t>
         </is>
       </c>
+      <c r="G396" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="397">
       <c r="A397" t="n">
@@ -13370,6 +16264,14 @@
           <t>胸を張って生きれば</t>
         </is>
       </c>
+      <c r="G404" t="n">
+        <v>1</v>
+      </c>
+      <c r="H404" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
     </row>
     <row r="405">
       <c r="A405" t="n">
@@ -13396,6 +16298,9 @@
           <t>最強なんだ</t>
         </is>
       </c>
+      <c r="G405" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="406">
       <c r="A406" t="n">
@@ -13474,6 +16379,14 @@
           <t>不可能の文字</t>
         </is>
       </c>
+      <c r="G408" t="n">
+        <v>1</v>
+      </c>
+      <c r="H408" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
     </row>
     <row r="409">
       <c r="A409" t="n">
@@ -13500,6 +16413,9 @@
           <t>オモイで吹き消したら</t>
         </is>
       </c>
+      <c r="G409" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="410">
       <c r="A410" t="n">
@@ -13552,6 +16468,14 @@
           <t>歌うんだ</t>
         </is>
       </c>
+      <c r="G411" t="n">
+        <v>1</v>
+      </c>
+      <c r="H411" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
     </row>
     <row r="412">
       <c r="A412" t="n">
@@ -13578,6 +16502,9 @@
           <t>（大きな声で）</t>
         </is>
       </c>
+      <c r="G412" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="413">
       <c r="A413" t="n">
@@ -13604,6 +16531,14 @@
           <t>あなたに</t>
         </is>
       </c>
+      <c r="G413" t="n">
+        <v>1</v>
+      </c>
+      <c r="H413" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
     </row>
     <row r="414">
       <c r="A414" t="n">
@@ -13630,6 +16565,9 @@
           <t>（届けたいから）</t>
         </is>
       </c>
+      <c r="G414" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="415">
       <c r="A415" t="n">
@@ -13656,6 +16594,14 @@
           <t>あなたに</t>
         </is>
       </c>
+      <c r="G415" t="n">
+        <v>1</v>
+      </c>
+      <c r="H415" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
     </row>
     <row r="416">
       <c r="A416" t="n">
@@ -13682,6 +16628,9 @@
           <t>（伝えたいから）</t>
         </is>
       </c>
+      <c r="G416" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="417">
       <c r="A417" t="n">
@@ -13786,6 +16735,9 @@
           <t>セカイに</t>
         </is>
       </c>
+      <c r="G420" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="421">
       <c r="A421" t="n">
@@ -13812,6 +16764,9 @@
           <t>走るセンセーション</t>
         </is>
       </c>
+      <c r="G421" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="422">
       <c r="A422" t="n">
@@ -13838,6 +16793,9 @@
           <t>満天の星ぎゅっと</t>
         </is>
       </c>
+      <c r="G422" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="423">
       <c r="A423" t="n">
@@ -13864,6 +16822,9 @@
           <t>抱きしめ</t>
         </is>
       </c>
+      <c r="G423" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="424">
       <c r="A424" t="n">
@@ -13890,6 +16851,9 @@
           <t>旅に出よう</t>
         </is>
       </c>
+      <c r="G424" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="425">
       <c r="A425" t="n">
@@ -13916,6 +16880,9 @@
           <t>全宇宙巻き込んで</t>
         </is>
       </c>
+      <c r="G425" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="426">
       <c r="A426" t="n">
@@ -13942,6 +16909,9 @@
           <t>いっちょ突破</t>
         </is>
       </c>
+      <c r="G426" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="427">
       <c r="A427" t="n">
@@ -13968,6 +16938,14 @@
           <t>刺されインテンション</t>
         </is>
       </c>
+      <c r="G427" t="n">
+        <v>1</v>
+      </c>
+      <c r="H427" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
     </row>
     <row r="428">
       <c r="A428" t="n">
@@ -13994,6 +16972,9 @@
           <t>めーいっぱいにとばせ</t>
         </is>
       </c>
+      <c r="G428" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="429">
       <c r="A429" t="n">
@@ -14358,6 +17339,14 @@
           <t>ああ意味ないや</t>
         </is>
       </c>
+      <c r="G442" t="n">
+        <v>1</v>
+      </c>
+      <c r="H442" t="inlineStr">
+        <is>
+          <t>half</t>
+        </is>
+      </c>
     </row>
     <row r="443">
       <c r="A443" t="n">
@@ -14384,6 +17373,9 @@
           <t>ラルラリラッタ</t>
         </is>
       </c>
+      <c r="G443" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="444">
       <c r="A444" t="n">
@@ -15036,6 +18028,14 @@
           <t>ここは遠く遠く描いた場所</t>
         </is>
       </c>
+      <c r="G468" t="n">
+        <v>1</v>
+      </c>
+      <c r="H468" t="inlineStr">
+        <is>
+          <t>half</t>
+        </is>
+      </c>
     </row>
     <row r="469">
       <c r="A469" t="n">
@@ -15062,6 +18062,9 @@
           <t>鼓動の音色を標せ</t>
         </is>
       </c>
+      <c r="G469" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="470">
       <c r="A470" t="n">
@@ -15533,6 +18536,14 @@
           <t>目が合えばなんでもわかるくらい</t>
         </is>
       </c>
+      <c r="G487" t="n">
+        <v>1</v>
+      </c>
+      <c r="H487" t="inlineStr">
+        <is>
+          <t>half</t>
+        </is>
+      </c>
     </row>
     <row r="488">
       <c r="A488" t="n">
@@ -15559,6 +18570,9 @@
           <t>大好きだよ</t>
         </is>
       </c>
+      <c r="G488" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="489">
       <c r="A489" t="n">
@@ -15977,6 +18991,14 @@
           <t>私##運命のドアを開いたの</t>
         </is>
       </c>
+      <c r="G504" t="n">
+        <v>1</v>
+      </c>
+      <c r="H504" t="inlineStr">
+        <is>
+          <t>insert</t>
+        </is>
+      </c>
     </row>
     <row r="505">
       <c r="A505" t="n">
@@ -16003,6 +19025,9 @@
           <t>（私）</t>
         </is>
       </c>
+      <c r="G505" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="506">
       <c r="A506" t="n">
@@ -16081,6 +19106,14 @@
           <t>困ってたら</t>
         </is>
       </c>
+      <c r="G508" t="n">
+        <v>1</v>
+      </c>
+      <c r="H508" t="inlineStr">
+        <is>
+          <t>half</t>
+        </is>
+      </c>
     </row>
     <row r="509">
       <c r="A509" t="n">
@@ -16107,6 +19140,9 @@
           <t>これからも助け合っていこうな</t>
         </is>
       </c>
+      <c r="G509" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="510">
       <c r="A510" t="n">
@@ -16289,6 +19325,14 @@
           <t>甘い愛には</t>
         </is>
       </c>
+      <c r="G516" t="n">
+        <v>1</v>
+      </c>
+      <c r="H516" t="inlineStr">
+        <is>
+          <t>half</t>
+        </is>
+      </c>
     </row>
     <row r="517">
       <c r="A517" t="n">
@@ -16315,6 +19359,9 @@
           <t>罠があるのよ</t>
         </is>
       </c>
+      <c r="G517" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="518">
       <c r="A518" t="n">
@@ -16393,6 +19440,14 @@
           <t>笑いかけて</t>
         </is>
       </c>
+      <c r="G520" t="n">
+        <v>1</v>
+      </c>
+      <c r="H520" t="inlineStr">
+        <is>
+          <t>half</t>
+        </is>
+      </c>
     </row>
     <row r="521">
       <c r="A521" t="n">
@@ -16419,6 +19474,9 @@
           <t>誘い出して</t>
         </is>
       </c>
+      <c r="G521" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="522">
       <c r="A522" t="n">
@@ -16445,6 +19503,14 @@
           <t>キミの心は</t>
         </is>
       </c>
+      <c r="G522" t="n">
+        <v>1</v>
+      </c>
+      <c r="H522" t="inlineStr">
+        <is>
+          <t>half</t>
+        </is>
+      </c>
     </row>
     <row r="523">
       <c r="A523" t="n">
@@ -16471,6 +19537,9 @@
           <t>シュガーレスガール</t>
         </is>
       </c>
+      <c r="G523" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="524">
       <c r="A524" t="n">
@@ -16682,6 +19751,14 @@
           <t>甘い愛には</t>
         </is>
       </c>
+      <c r="G531" t="n">
+        <v>1</v>
+      </c>
+      <c r="H531" t="inlineStr">
+        <is>
+          <t>half</t>
+        </is>
+      </c>
     </row>
     <row r="532">
       <c r="A532" t="n">
@@ -16708,6 +19785,9 @@
           <t>罠があるのよ</t>
         </is>
       </c>
+      <c r="G532" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="533">
       <c r="A533" t="n">
@@ -16786,6 +19866,14 @@
           <t>笑いかけて</t>
         </is>
       </c>
+      <c r="G535" t="n">
+        <v>1</v>
+      </c>
+      <c r="H535" t="inlineStr">
+        <is>
+          <t>half</t>
+        </is>
+      </c>
     </row>
     <row r="536">
       <c r="A536" t="n">
@@ -16812,6 +19900,9 @@
           <t>誘い出して</t>
         </is>
       </c>
+      <c r="G536" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="537">
       <c r="A537" t="n">
@@ -16838,6 +19929,14 @@
           <t>キミの心は</t>
         </is>
       </c>
+      <c r="G537" t="n">
+        <v>1</v>
+      </c>
+      <c r="H537" t="inlineStr">
+        <is>
+          <t>half</t>
+        </is>
+      </c>
     </row>
     <row r="538">
       <c r="A538" t="n">
@@ -16864,6 +19963,9 @@
           <t>シュガーレスガール</t>
         </is>
       </c>
+      <c r="G538" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="539">
       <c r="A539" t="n">
@@ -16890,6 +19992,14 @@
           <t>きっと</t>
         </is>
       </c>
+      <c r="G539" t="n">
+        <v>1</v>
+      </c>
+      <c r="H539" t="inlineStr">
+        <is>
+          <t>half</t>
+        </is>
+      </c>
     </row>
     <row r="540">
       <c r="A540" t="n">
@@ -16916,6 +20026,9 @@
           <t>今どこかで 最悪な事があって</t>
         </is>
       </c>
+      <c r="G540" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="541">
       <c r="A541" t="n">
@@ -17126,6 +20239,14 @@
           <t>甘い愛には</t>
         </is>
       </c>
+      <c r="G548" t="n">
+        <v>1</v>
+      </c>
+      <c r="H548" t="inlineStr">
+        <is>
+          <t>half</t>
+        </is>
+      </c>
     </row>
     <row r="549">
       <c r="A549" t="n">
@@ -17152,6 +20273,9 @@
           <t>罠があるのよ</t>
         </is>
       </c>
+      <c r="G549" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="550">
       <c r="A550" t="n">
@@ -17230,6 +20354,14 @@
           <t>笑いかけて</t>
         </is>
       </c>
+      <c r="G552" t="n">
+        <v>1</v>
+      </c>
+      <c r="H552" t="inlineStr">
+        <is>
+          <t>half</t>
+        </is>
+      </c>
     </row>
     <row r="553">
       <c r="A553" t="n">
@@ -17256,6 +20388,9 @@
           <t>誘い出して</t>
         </is>
       </c>
+      <c r="G553" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="554">
       <c r="A554" t="n">
@@ -17282,6 +20417,14 @@
           <t>キミの心は</t>
         </is>
       </c>
+      <c r="G554" t="n">
+        <v>1</v>
+      </c>
+      <c r="H554" t="inlineStr">
+        <is>
+          <t>half</t>
+        </is>
+      </c>
     </row>
     <row r="555">
       <c r="A555" t="n">
@@ -17308,6 +20451,9 @@
           <t>シュガーレスガール</t>
         </is>
       </c>
+      <c r="G555" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="556">
       <c r="A556" t="n">
@@ -17492,6 +20638,9 @@
           <t>鮮やかに</t>
         </is>
       </c>
+      <c r="G562" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="563">
       <c r="A563" t="n">
@@ -17518,6 +20667,9 @@
           <t>焼き付ける憧れのImageを</t>
         </is>
       </c>
+      <c r="G563" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="564">
       <c r="A564" t="n">
@@ -17544,6 +20696,9 @@
           <t>与えたい</t>
         </is>
       </c>
+      <c r="G564" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="565">
       <c r="A565" t="n">
@@ -17570,6 +20725,9 @@
           <t>私という存在を</t>
         </is>
       </c>
+      <c r="G565" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="566">
       <c r="A566" t="n">
@@ -17908,6 +21066,9 @@
           <t>鮮やかに</t>
         </is>
       </c>
+      <c r="G578" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="579">
       <c r="A579" t="n">
@@ -17934,6 +21095,9 @@
           <t>裏切って期待以上のShowを</t>
         </is>
       </c>
+      <c r="G579" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="580">
       <c r="A580" t="n">
@@ -17960,6 +21124,9 @@
           <t>頑張りは</t>
         </is>
       </c>
+      <c r="G580" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="581">
       <c r="A581" t="n">
@@ -17986,6 +21153,9 @@
           <t>隠すのがクールでしょ？</t>
         </is>
       </c>
+      <c r="G581" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="582">
       <c r="A582" t="n">
@@ -18326,6 +21496,14 @@
           <t>そう乱反射する</t>
         </is>
       </c>
+      <c r="G594" t="n">
+        <v>1</v>
+      </c>
+      <c r="H594" t="inlineStr">
+        <is>
+          <t>half</t>
+        </is>
+      </c>
     </row>
     <row r="595">
       <c r="A595" t="n">
@@ -18352,6 +21530,9 @@
           <t>可能性を掴むImage</t>
         </is>
       </c>
+      <c r="G595" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="596">
       <c r="A596" t="n">
@@ -18378,6 +21559,14 @@
           <t>忘れない</t>
         </is>
       </c>
+      <c r="G596" t="n">
+        <v>1</v>
+      </c>
+      <c r="H596" t="inlineStr">
+        <is>
+          <t>half</t>
+        </is>
+      </c>
     </row>
     <row r="597">
       <c r="A597" t="n">
@@ -18404,6 +21593,9 @@
           <t>もしも波に呑まれても</t>
         </is>
       </c>
+      <c r="G597" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="598">
       <c r="A598" t="n">
@@ -18430,6 +21622,14 @@
           <t>迫るEmbark</t>
         </is>
       </c>
+      <c r="G598" t="n">
+        <v>1</v>
+      </c>
+      <c r="H598" t="inlineStr">
+        <is>
+          <t>half</t>
+        </is>
+      </c>
     </row>
     <row r="599">
       <c r="A599" t="n">
@@ -18456,6 +21656,9 @@
           <t>弾けろSynapse</t>
         </is>
       </c>
+      <c r="G599" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="600">
       <c r="A600" t="n">
@@ -18690,6 +21893,14 @@
           <t>立ち上がれWe are Frontier</t>
         </is>
       </c>
+      <c r="G608" t="n">
+        <v>1</v>
+      </c>
+      <c r="H608" t="inlineStr">
+        <is>
+          <t>half</t>
+        </is>
+      </c>
     </row>
     <row r="609">
       <c r="A609" t="n">
@@ -18716,6 +21927,9 @@
           <t>戻れないけど大丈夫？</t>
         </is>
       </c>
+      <c r="G609" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="610">
       <c r="A610" t="n">
@@ -18846,6 +22060,14 @@
           <t>信じた道を</t>
         </is>
       </c>
+      <c r="G614" t="n">
+        <v>1</v>
+      </c>
+      <c r="H614" t="inlineStr">
+        <is>
+          <t>half</t>
+        </is>
+      </c>
     </row>
     <row r="615">
       <c r="A615" t="n">
@@ -18872,6 +22094,14 @@
           <t>思うままに</t>
         </is>
       </c>
+      <c r="G615" t="n">
+        <v>2</v>
+      </c>
+      <c r="H615" t="inlineStr">
+        <is>
+          <t>half</t>
+        </is>
+      </c>
     </row>
     <row r="616">
       <c r="A616" t="n">
@@ -18898,6 +22128,9 @@
           <t>切り拓こう</t>
         </is>
       </c>
+      <c r="G616" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="617">
       <c r="A617" t="n">
@@ -21467,6 +24700,9 @@
           <t>そんなことぜんぶお見通しです、</t>
         </is>
       </c>
+      <c r="G713" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="714">
       <c r="A714" t="n">
@@ -21493,6 +24729,9 @@
           <t>だって逆に</t>
         </is>
       </c>
+      <c r="G714" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="715">
       <c r="A715" t="n">
@@ -22181,6 +25420,9 @@
           <t>祝福の</t>
         </is>
       </c>
+      <c r="G740" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="741">
       <c r="A741" t="n">
@@ -22207,6 +25449,9 @@
           <t>鐘のように</t>
         </is>
       </c>
+      <c r="G741" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="742">
       <c r="A742" t="n">
@@ -22234,6 +25479,9 @@
 ハピネスじゃん！</t>
         </is>
       </c>
+      <c r="G742" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="743">
       <c r="A743" t="n">
@@ -23645,6 +26893,9 @@
           <t>傷つけないと　いつか</t>
         </is>
       </c>
+      <c r="G795" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="796">
       <c r="A796" t="n">
@@ -23671,6 +26922,9 @@
           <t>このまま</t>
         </is>
       </c>
+      <c r="G796" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="797">
       <c r="A797" t="n">
@@ -23697,6 +26951,9 @@
           <t>傷つけられると　カルマ</t>
         </is>
       </c>
+      <c r="G797" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="798">
       <c r="A798" t="n">
@@ -23722,6 +26979,9 @@
         <is>
           <t>終わらない</t>
         </is>
+      </c>
+      <c r="G798" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="799">
@@ -24146,6 +27406,9 @@
           <t>誰かを裏返して</t>
         </is>
       </c>
+      <c r="G814" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="815">
       <c r="A815" t="n">
@@ -24172,6 +27435,14 @@
           <t>揃えて</t>
         </is>
       </c>
+      <c r="G815" t="n">
+        <v>2</v>
+      </c>
+      <c r="H815" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
     </row>
     <row r="816">
       <c r="A816" t="n">
@@ -24198,6 +27469,9 @@
           <t>正しくあろうだなんて</t>
         </is>
       </c>
+      <c r="G816" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="817">
       <c r="A817" t="n">
@@ -24224,6 +27498,14 @@
           <t>まちがい</t>
         </is>
       </c>
+      <c r="G817" t="n">
+        <v>2</v>
+      </c>
+      <c r="H817" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
     </row>
     <row r="818">
       <c r="A818" t="n">
@@ -25011,6 +28293,9 @@
           <t>私は</t>
         </is>
       </c>
+      <c r="G847" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="848">
       <c r="A848" t="n">
@@ -25037,6 +28322,9 @@
           <t>砕けない</t>
         </is>
       </c>
+      <c r="G848" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="849">
       <c r="A849" t="n">
@@ -25170,6 +28458,9 @@
           <t>言えない気持ちと　ねぇ</t>
         </is>
       </c>
+      <c r="G853" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="854">
       <c r="A854" t="n">
@@ -25196,6 +28487,14 @@
           <t>同じくらい</t>
         </is>
       </c>
+      <c r="G854" t="n">
+        <v>2</v>
+      </c>
+      <c r="H854" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
     </row>
     <row r="855">
       <c r="A855" t="n">
@@ -25222,6 +28521,14 @@
           <t>しゅんっと消えちゃうんだって</t>
         </is>
       </c>
+      <c r="G855" t="n">
+        <v>3</v>
+      </c>
+      <c r="H855" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
     </row>
     <row r="856">
       <c r="A856" t="n">
@@ -25352,6 +28659,9 @@
           <t>キミ。</t>
         </is>
       </c>
+      <c r="G860" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="861">
       <c r="A861" t="n">
@@ -25378,6 +28688,9 @@
           <t>体温　感じたいの</t>
         </is>
       </c>
+      <c r="G861" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="862">
       <c r="A862" t="n">
@@ -25588,6 +28901,9 @@
           <t>なんて　妄想するだけの未来？</t>
         </is>
       </c>
+      <c r="G869" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="870">
       <c r="A870" t="n">
@@ -25614,6 +28930,14 @@
           <t>気づいてくれないかなぁ</t>
         </is>
       </c>
+      <c r="G870" t="n">
+        <v>2</v>
+      </c>
+      <c r="H870" t="inlineStr">
+        <is>
+          <t>half</t>
+        </is>
+      </c>
     </row>
     <row r="871">
       <c r="A871" t="n">
@@ -25640,6 +28964,9 @@
           <t>長いまつ毛と</t>
         </is>
       </c>
+      <c r="G871" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="872">
       <c r="A872" t="n">
@@ -25666,6 +28993,14 @@
           <t>あざといリップの女友達(あのこたち)</t>
         </is>
       </c>
+      <c r="G872" t="n">
+        <v>2</v>
+      </c>
+      <c r="H872" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
     </row>
     <row r="873">
       <c r="A873" t="n">
@@ -25718,6 +29053,9 @@
           <t>鈍感過ぎ！ でも好き</t>
         </is>
       </c>
+      <c r="G874" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="875">
       <c r="A875" t="n">
@@ -25744,6 +29082,14 @@
           <t>不意打ち　どきゅん</t>
         </is>
       </c>
+      <c r="G875" t="n">
+        <v>2</v>
+      </c>
+      <c r="H875" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
     </row>
     <row r="876">
       <c r="A876" t="n">
@@ -25770,6 +29116,14 @@
           <t>バキュン！</t>
         </is>
       </c>
+      <c r="G876" t="n">
+        <v>3</v>
+      </c>
+      <c r="H876" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
     </row>
     <row r="877">
       <c r="A877" t="n">
@@ -25796,6 +29150,14 @@
           <t>狙い撃ちですっ</t>
         </is>
       </c>
+      <c r="G877" t="n">
+        <v>4</v>
+      </c>
+      <c r="H877" t="inlineStr">
+        <is>
+          <t>half</t>
+        </is>
+      </c>
     </row>
     <row r="878">
       <c r="A878" t="n">
@@ -25848,6 +29210,9 @@
           <t>テンション！</t>
         </is>
       </c>
+      <c r="G879" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="880">
       <c r="A880" t="n">
@@ -25874,6 +29239,14 @@
           <t>どんどん高鳴ってる</t>
         </is>
       </c>
+      <c r="G880" t="n">
+        <v>2</v>
+      </c>
+      <c r="H880" t="inlineStr">
+        <is>
+          <t>half</t>
+        </is>
+      </c>
     </row>
     <row r="881">
       <c r="A881" t="n">
@@ -25900,6 +29273,9 @@
           <t>純真！</t>
         </is>
       </c>
+      <c r="G881" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="882">
       <c r="A882" t="n">
@@ -25926,6 +29302,14 @@
           <t>輝いて舞い降りたんだ「大好き。」が　もう少し....近くで</t>
         </is>
       </c>
+      <c r="G882" t="n">
+        <v>2</v>
+      </c>
+      <c r="H882" t="inlineStr">
+        <is>
+          <t>half</t>
+        </is>
+      </c>
     </row>
     <row r="883">
       <c r="A883" t="n">
@@ -26189,6 +29573,9 @@
           <t>未来へ描く軌跡は</t>
         </is>
       </c>
+      <c r="G892" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="893">
       <c r="A893" t="n">
@@ -26215,6 +29602,14 @@
           <t>(Shooting Stars)</t>
         </is>
       </c>
+      <c r="G893" t="n">
+        <v>2</v>
+      </c>
+      <c r="H893" t="inlineStr">
+        <is>
+          <t>half</t>
+        </is>
+      </c>
     </row>
     <row r="894">
       <c r="A894" t="n">
@@ -26501,6 +29896,9 @@
           <t>喜怒哀楽　気分</t>
         </is>
       </c>
+      <c r="G904" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="905">
       <c r="A905" t="n">
@@ -26527,6 +29925,9 @@
           <t>Up and Down</t>
         </is>
       </c>
+      <c r="G905" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="906">
       <c r="A906" t="n">
@@ -26631,6 +30032,9 @@
           <t>奇想天外</t>
         </is>
       </c>
+      <c r="G909" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="910">
       <c r="A910" t="n">
@@ -26657,6 +30061,14 @@
           <t>is サプライズ</t>
         </is>
       </c>
+      <c r="G910" t="n">
+        <v>2</v>
+      </c>
+      <c r="H910" t="inlineStr">
+        <is>
+          <t>half</t>
+        </is>
+      </c>
     </row>
     <row r="911">
       <c r="A911" t="n">
@@ -27178,6 +30590,9 @@
           <t>どこまでも行ける</t>
         </is>
       </c>
+      <c r="G930" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="931">
       <c r="A931" t="n">
@@ -27204,6 +30619,14 @@
           <t>どこへでも行ける</t>
         </is>
       </c>
+      <c r="G931" t="n">
+        <v>2</v>
+      </c>
+      <c r="H931" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
     </row>
     <row r="932">
       <c r="A932" t="n">
@@ -27230,6 +30653,9 @@
           <t>遥か彼方へ</t>
         </is>
       </c>
+      <c r="G932" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="933">
       <c r="A933" t="n">
@@ -27256,6 +30682,14 @@
           <t>続く</t>
         </is>
       </c>
+      <c r="G933" t="n">
+        <v>2</v>
+      </c>
+      <c r="H933" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
     </row>
     <row r="934">
       <c r="A934" t="n">
@@ -27543,6 +30977,9 @@
           <t>未来へ描く軌跡は</t>
         </is>
       </c>
+      <c r="G944" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="945">
       <c r="A945" t="n">
@@ -27569,6 +31006,14 @@
           <t>(Shooting Stars)</t>
         </is>
       </c>
+      <c r="G945" t="n">
+        <v>2</v>
+      </c>
+      <c r="H945" t="inlineStr">
+        <is>
+          <t>half</t>
+        </is>
+      </c>
     </row>
     <row r="946">
       <c r="A946" t="n">
@@ -27699,6 +31144,9 @@
           <t>はちゃめちゃわちゃっと</t>
         </is>
       </c>
+      <c r="G950" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="951">
       <c r="A951" t="n">
@@ -27725,6 +31173,14 @@
           <t>Wah！どぅわちゃらいっ！</t>
         </is>
       </c>
+      <c r="G951" t="n">
+        <v>2</v>
+      </c>
+      <c r="H951" t="inlineStr">
+        <is>
+          <t>half</t>
+        </is>
+      </c>
     </row>
     <row r="952">
       <c r="A952" t="n">
@@ -27777,6 +31233,9 @@
           <t>はーい　さあみんなあそぼう</t>
         </is>
       </c>
+      <c r="G953" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="954">
       <c r="A954" t="n">
@@ -27803,6 +31262,14 @@
           <t>この指止まれ</t>
         </is>
       </c>
+      <c r="G954" t="n">
+        <v>2</v>
+      </c>
+      <c r="H954" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
     </row>
     <row r="955">
       <c r="A955" t="n">
@@ -27855,6 +31322,9 @@
           <t>チャーミングにみんな今日も</t>
         </is>
       </c>
+      <c r="G956" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="957">
       <c r="A957" t="n">
@@ -27881,6 +31351,9 @@
           <t>いい感じ</t>
         </is>
       </c>
+      <c r="G957" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="958">
       <c r="A958" t="n">
@@ -27907,6 +31380,9 @@
           <t>(Fu)</t>
         </is>
       </c>
+      <c r="G958" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="959">
       <c r="A959" t="n">
@@ -27985,6 +31461,9 @@
           <t>カワイイとこも</t>
         </is>
       </c>
+      <c r="G961" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="962">
       <c r="A962" t="n">
@@ -28011,6 +31490,14 @@
           <t>おバカなとこも</t>
         </is>
       </c>
+      <c r="G962" t="n">
+        <v>2</v>
+      </c>
+      <c r="H962" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
     </row>
     <row r="963">
       <c r="A963" t="n">
@@ -28037,6 +31524,9 @@
           <t>ぎゅっと愛するべき</t>
         </is>
       </c>
+      <c r="G963" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="964">
       <c r="A964" t="n">
@@ -28063,6 +31553,9 @@
           <t>推しポイント</t>
         </is>
       </c>
+      <c r="G964" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="965">
       <c r="A965" t="n">
@@ -28089,6 +31582,9 @@
           <t>だゾ</t>
         </is>
       </c>
+      <c r="G965" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="966">
       <c r="A966" t="n">
@@ -28401,6 +31897,9 @@
           <t>はちゃめちゃわちゃっと</t>
         </is>
       </c>
+      <c r="G977" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="978">
       <c r="A978" t="n">
@@ -28427,6 +31926,14 @@
           <t>Wah！どぅわちゃらいっ！</t>
         </is>
       </c>
+      <c r="G978" t="n">
+        <v>2</v>
+      </c>
+      <c r="H978" t="inlineStr">
+        <is>
+          <t>half</t>
+        </is>
+      </c>
     </row>
     <row r="979">
       <c r="A979" t="n">
@@ -28531,6 +32038,9 @@
           <t>どんな君も</t>
         </is>
       </c>
+      <c r="G982" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="983">
       <c r="A983" t="n">
@@ -28557,6 +32067,14 @@
           <t>どぅわどぅわどぅわちゃらいっ！</t>
         </is>
       </c>
+      <c r="G983" t="n">
+        <v>2</v>
+      </c>
+      <c r="H983" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
     </row>
     <row r="984">
       <c r="A984" t="n">
@@ -28583,6 +32101,9 @@
           <t>毎日　毎毎日 Do what you like</t>
         </is>
       </c>
+      <c r="G984" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="985">
       <c r="A985" t="n">
@@ -28609,6 +32130,9 @@
           <t>(Fu Fu)</t>
         </is>
       </c>
+      <c r="G985" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="986">
       <c r="A986" t="n">
@@ -28635,6 +32159,9 @@
           <t>大好き　大大好き Do what you like</t>
         </is>
       </c>
+      <c r="G986" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="987">
       <c r="A987" t="n">
@@ -28661,6 +32188,9 @@
           <t>(Fu Fu)</t>
         </is>
       </c>
+      <c r="G987" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="988">
       <c r="A988" t="n">
@@ -28687,6 +32217,9 @@
           <t>胸がいっぱい　いっぱい Do what you like</t>
         </is>
       </c>
+      <c r="G988" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="989">
       <c r="A989" t="n">
@@ -28713,6 +32246,9 @@
           <t>(Fu Fu)</t>
         </is>
       </c>
+      <c r="G989" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="990">
       <c r="A990" t="n">
@@ -28765,6 +32301,9 @@
           <t>お兄さんもお姉さんも</t>
         </is>
       </c>
+      <c r="G991" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="992">
       <c r="A992" t="n">
@@ -28791,6 +32330,14 @@
           <t>わちゃライフ！わちゃライフ！</t>
         </is>
       </c>
+      <c r="G992" t="n">
+        <v>2</v>
+      </c>
+      <c r="H992" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
     </row>
     <row r="993">
       <c r="A993" t="n">
@@ -28817,6 +32364,9 @@
           <t>呑気もお天気も</t>
         </is>
       </c>
+      <c r="G993" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="994">
       <c r="A994" t="n">
@@ -28843,6 +32393,14 @@
           <t>わちゃライフ！わちゃライフ！</t>
         </is>
       </c>
+      <c r="G994" t="n">
+        <v>2</v>
+      </c>
+      <c r="H994" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
     </row>
     <row r="995">
       <c r="A995" t="n">
@@ -28869,6 +32427,9 @@
           <t>3にも4にも</t>
         </is>
       </c>
+      <c r="G995" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="996">
       <c r="A996" t="n">
@@ -28895,6 +32456,14 @@
           <t>わちゃライフ！わちゃライフ！</t>
         </is>
       </c>
+      <c r="G996" t="n">
+        <v>2</v>
+      </c>
+      <c r="H996" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
     </row>
     <row r="997">
       <c r="A997" t="n">
@@ -29155,6 +32724,9 @@
           <t>得意も不得意も　得手も苦手も</t>
         </is>
       </c>
+      <c r="G1006" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="1007">
       <c r="A1007" t="n">
@@ -29181,6 +32753,14 @@
           <t>全部君のチャームポイント</t>
         </is>
       </c>
+      <c r="G1007" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1007" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
     </row>
     <row r="1008">
       <c r="A1008" t="n">
@@ -29207,6 +32787,9 @@
           <t>晴れのち雨も　雨のち晴れも</t>
         </is>
       </c>
+      <c r="G1008" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="1009">
       <c r="A1009" t="n">
@@ -29233,6 +32816,14 @@
           <t>どっちだって構わない</t>
         </is>
       </c>
+      <c r="G1009" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1009" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
     </row>
     <row r="1010">
       <c r="A1010" t="n">
@@ -29467,6 +33058,9 @@
           <t>じゃ、そゆことで</t>
         </is>
       </c>
+      <c r="G1018" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="1019">
       <c r="A1019" t="n">
@@ -29493,6 +33087,9 @@
           <t>(Yeah！)</t>
         </is>
       </c>
+      <c r="G1019" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="1020">
       <c r="A1020" t="n">
@@ -29805,6 +33402,9 @@
           <t>はちゃめちゃわちゃっと</t>
         </is>
       </c>
+      <c r="G1031" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="1032">
       <c r="A1032" t="n">
@@ -29831,6 +33431,14 @@
           <t>Wah！どぅわちゃらいっ！</t>
         </is>
       </c>
+      <c r="G1032" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1032" t="inlineStr">
+        <is>
+          <t>half</t>
+        </is>
+      </c>
     </row>
     <row r="1033">
       <c r="A1033" t="n">
@@ -29913,6 +33521,9 @@
 ラブストーリーとか、</t>
         </is>
       </c>
+      <c r="G1035" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="1036">
       <c r="A1036" t="n">
@@ -29940,6 +33551,9 @@
 本命なんだし</t>
         </is>
       </c>
+      <c r="G1036" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="1037">
       <c r="A1037" t="n">
@@ -29993,6 +33607,9 @@
           <t>大人になったって、</t>
         </is>
       </c>
+      <c r="G1038" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="1039">
       <c r="A1039" t="n">
@@ -30019,6 +33636,9 @@
           <t>ドキドキしてたいもんだって</t>
         </is>
       </c>
+      <c r="G1039" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="1040">
       <c r="A1040" t="n">
@@ -30151,6 +33771,9 @@
 一年で</t>
         </is>
       </c>
+      <c r="G1044" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="1045">
       <c r="A1045" t="n">
@@ -30177,6 +33800,9 @@
           <t>一番の贅沢でもしちゃいましょうよ</t>
         </is>
       </c>
+      <c r="G1045" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="1046">
       <c r="A1046" t="n">
@@ -30204,6 +33830,9 @@
 ちょこっとは</t>
         </is>
       </c>
+      <c r="G1046" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="1047">
       <c r="A1047" t="n">
@@ -30230,6 +33859,9 @@
           <t>予算とカロリーとかはオーバーでもね</t>
         </is>
       </c>
+      <c r="G1047" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="1048">
       <c r="A1048" t="n">
@@ -30365,6 +33997,9 @@
 そりゃそうだけどね、</t>
         </is>
       </c>
+      <c r="G1052" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="1053">
       <c r="A1053" t="n">
@@ -30392,6 +34027,9 @@
 それも変かな</t>
         </is>
       </c>
+      <c r="G1053" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="1054">
       <c r="A1054" t="n">
@@ -30445,6 +34083,9 @@
           <t>でもあれわたしが、</t>
         </is>
       </c>
+      <c r="G1055" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="1056">
       <c r="A1056" t="n">
@@ -30471,6 +34112,9 @@
           <t>ほしかったかわいいやつじゃない？</t>
         </is>
       </c>
+      <c r="G1056" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="1057">
       <c r="A1057" t="n">
@@ -30603,6 +34247,9 @@
 そんなこと</t>
         </is>
       </c>
+      <c r="G1061" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="1062">
       <c r="A1062" t="n">
@@ -30629,6 +34276,9 @@
           <t>想像もしてなかったの、眠れないね</t>
         </is>
       </c>
+      <c r="G1062" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="1063">
       <c r="A1063" t="n">
@@ -30814,6 +34464,9 @@
 一年で</t>
         </is>
       </c>
+      <c r="G1069" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="1070">
       <c r="A1070" t="n">
@@ -30840,6 +34493,9 @@
           <t>一番の贅沢でもしよ</t>
         </is>
       </c>
+      <c r="G1070" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="1071">
       <c r="A1071" t="n">
@@ -30946,6 +34602,9 @@
 一年で</t>
         </is>
       </c>
+      <c r="G1074" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="1075">
       <c r="A1075" t="n">
@@ -30972,6 +34631,9 @@
           <t>一番の贅沢でもしちゃいましょうよ</t>
         </is>
       </c>
+      <c r="G1075" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="1076">
       <c r="A1076" t="n">
@@ -30999,6 +34661,9 @@
 ちょこっとは</t>
         </is>
       </c>
+      <c r="G1076" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="1077">
       <c r="A1077" t="n">
@@ -31024,6 +34689,9 @@
         <is>
           <t>予算とカロリーとかはオーバーでもね</t>
         </is>
+      </c>
+      <c r="G1077" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="1078">
@@ -31875,6 +35543,9 @@
           <t>あまネキ!</t>
         </is>
       </c>
+      <c r="G1109" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="1110">
       <c r="A1110" t="n">
@@ -31901,6 +35572,14 @@
           <t>にゃんこPPER!</t>
         </is>
       </c>
+      <c r="G1110" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1110" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
     </row>
     <row r="1111">
       <c r="A1111" t="n">
@@ -31927,6 +35606,9 @@
           <t>ノエちゃん!</t>
         </is>
       </c>
+      <c r="G1111" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="1112">
       <c r="A1112" t="n">
@@ -31953,6 +35635,14 @@
           <t>インテリPPER!</t>
         </is>
       </c>
+      <c r="G1112" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1112" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
     </row>
     <row r="1113">
       <c r="A1113" t="n">
@@ -31979,6 +35669,9 @@
           <t>ゆいちゃん!</t>
         </is>
       </c>
+      <c r="G1113" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="1114">
       <c r="A1114" t="n">
@@ -32005,6 +35698,14 @@
           <t>笑顔PPER!</t>
         </is>
       </c>
+      <c r="G1114" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1114" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
     </row>
     <row r="1115">
       <c r="A1115" t="n">
@@ -32031,6 +35732,9 @@
           <t>おすず!</t>
         </is>
       </c>
+      <c r="G1115" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="1116">
       <c r="A1116" t="n">
@@ -32057,6 +35761,14 @@
           <t>たらこPPER!</t>
         </is>
       </c>
+      <c r="G1116" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1116" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
     </row>
     <row r="1117">
       <c r="A1117" t="n">
@@ -32083,6 +35795,9 @@
           <t>まつかれ!</t>
         </is>
       </c>
+      <c r="G1117" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="1118">
       <c r="A1118" t="n">
@@ -32109,6 +35824,14 @@
           <t>ほっぺPPER!</t>
         </is>
       </c>
+      <c r="G1118" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1118" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
     </row>
     <row r="1119">
       <c r="A1119" t="n">
@@ -32135,6 +35858,9 @@
           <t>まなふぃ!</t>
         </is>
       </c>
+      <c r="G1119" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="1120">
       <c r="A1120" t="n">
@@ -32161,6 +35887,14 @@
           <t>きんにくPPER!</t>
         </is>
       </c>
+      <c r="G1120" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1120" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
     </row>
     <row r="1121">
       <c r="A1121" t="n">
@@ -32187,6 +35921,9 @@
           <t>るなぴ!</t>
         </is>
       </c>
+      <c r="G1121" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="1122">
       <c r="A1122" t="n">
@@ -32211,6 +35948,14 @@
       <c r="F1122" t="inlineStr">
         <is>
           <t>ギャルPPER!</t>
+        </is>
+      </c>
+      <c r="G1122" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1122" t="inlineStr">
+        <is>
+          <t>full</t>
         </is>
       </c>
     </row>
@@ -35016,6 +38761,9 @@
           <t>LIFE IS THE PURENESS！</t>
         </is>
       </c>
+      <c r="G1229" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="1230">
       <c r="A1230" t="n">
@@ -35042,6 +38790,9 @@
           <t>LIFE IS THE PURENESS！</t>
         </is>
       </c>
+      <c r="G1230" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="1231">
       <c r="A1231" t="n">
@@ -35094,6 +38845,9 @@
           <t>LIFE IS THE PURENESS！</t>
         </is>
       </c>
+      <c r="G1232" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="1233">
       <c r="A1233" t="n">
@@ -35120,6 +38874,9 @@
           <t>LIFE IS THE PURENESS！</t>
         </is>
       </c>
+      <c r="G1233" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="1234">
       <c r="A1234" t="n">
@@ -35172,6 +38929,9 @@
           <t>LIFE IS THE PURENESS！</t>
         </is>
       </c>
+      <c r="G1235" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="1236">
       <c r="A1236" t="n">
@@ -35198,6 +38958,9 @@
           <t>LIFE IS THE PURENESS！</t>
         </is>
       </c>
+      <c r="G1236" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="1237">
       <c r="A1237" t="n">
@@ -35250,6 +39013,9 @@
           <t>LIFE IS THE PURENESS！</t>
         </is>
       </c>
+      <c r="G1238" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="1239">
       <c r="A1239" t="n">
@@ -35276,6 +39042,9 @@
           <t>LIFE IS THE PURENESS！</t>
         </is>
       </c>
+      <c r="G1239" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="1240">
       <c r="A1240" t="n">
@@ -35647,6 +39416,9 @@
           <t>それがなんであっても、</t>
         </is>
       </c>
+      <c r="G1253" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="1254">
       <c r="A1254" t="n">
@@ -35674,6 +39446,9 @@
 愛される、今日も</t>
         </is>
       </c>
+      <c r="G1254" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="1255">
       <c r="A1255" t="n">
@@ -35727,6 +39502,9 @@
           <t>ああ、美しく育った</t>
         </is>
       </c>
+      <c r="G1256" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="1257">
       <c r="A1257" t="n">
@@ -35753,6 +39531,9 @@
           <t>空よりまぶしい、恋よりまぶしい人生</t>
         </is>
       </c>
+      <c r="G1257" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="1258">
       <c r="A1258" t="n">
@@ -35993,6 +39774,9 @@
           <t>たまにそれに飽きても、</t>
         </is>
       </c>
+      <c r="G1266" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="1267">
       <c r="A1267" t="n">
@@ -36020,6 +39804,9 @@
 愛されるだろう</t>
         </is>
       </c>
+      <c r="G1267" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="1268">
       <c r="A1268" t="n">
@@ -36073,6 +39860,9 @@
           <t>ああ、限りなく透明な</t>
         </is>
       </c>
+      <c r="G1269" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="1270">
       <c r="A1270" t="n">
@@ -36099,6 +39889,9 @@
           <t>空より尊い、恋より尊い運命</t>
         </is>
       </c>
+      <c r="G1270" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="1271">
       <c r="A1271" t="n">
@@ -36310,6 +40103,9 @@
           <t>ああ、美しく育った</t>
         </is>
       </c>
+      <c r="G1278" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="1279">
       <c r="A1279" t="n">
@@ -36336,6 +40132,9 @@
           <t>空よりまぶしい、恋よりまぶしい人生</t>
         </is>
       </c>
+      <c r="G1279" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="1280">
       <c r="A1280" t="n">
@@ -37834,6 +41633,9 @@
           <t>個性的なもぎたての</t>
         </is>
       </c>
+      <c r="G1335" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="1336">
       <c r="A1336" t="n">
@@ -37860,6 +41662,14 @@
           <t>フレッシュなフルーツ</t>
         </is>
       </c>
+      <c r="G1336" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1336" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
     </row>
     <row r="1337">
       <c r="A1337" t="n">
@@ -38122,6 +41932,9 @@
           <t>この夏　いちばんの</t>
         </is>
       </c>
+      <c r="G1346" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="1347">
       <c r="A1347" t="n">
@@ -38148,6 +41961,9 @@
           <t>弾けそうなスタイルで</t>
         </is>
       </c>
+      <c r="G1347" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="1348">
       <c r="A1348" t="n">
@@ -38200,6 +42016,9 @@
           <t>決戦の瞬間(とき)が</t>
         </is>
       </c>
+      <c r="G1349" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="1350">
       <c r="A1350" t="n">
@@ -38226,6 +42045,14 @@
           <t>キター！</t>
         </is>
       </c>
+      <c r="G1350" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1350" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
     </row>
     <row r="1351">
       <c r="A1351" t="n">
@@ -38279,6 +42106,9 @@
           <t>声あげろ　ひと夏の約束</t>
         </is>
       </c>
+      <c r="G1352" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="1353">
       <c r="A1353" t="n">
@@ -38306,6 +42136,14 @@
 ままで　今　君はどこにいるの？</t>
         </is>
       </c>
+      <c r="G1353" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1353" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
     </row>
     <row r="1354">
       <c r="A1354" t="n">
@@ -38620,6 +42458,9 @@
           <t>Ah　火照ったカラダ　燃やそう</t>
         </is>
       </c>
+      <c r="G1365" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="1366">
       <c r="A1366" t="n">
@@ -38646,6 +42487,9 @@
           <t>(まだまだーー)</t>
         </is>
       </c>
+      <c r="G1366" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="1367">
       <c r="A1367" t="n">
@@ -38885,6 +42729,9 @@
           <t>中身は変わっていますので、その辺でも評価！</t>
         </is>
       </c>
+      <c r="G1375" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="1376">
       <c r="A1376" t="n">
@@ -38911,6 +42758,9 @@
           <t>(おねがい！)</t>
         </is>
       </c>
+      <c r="G1376" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="1377">
       <c r="A1377" t="n">
@@ -39410,6 +43260,9 @@
           <t>もっとわかりやすくていいんだよ、お待ちしてます</t>
         </is>
       </c>
+      <c r="G1395" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="1396">
       <c r="A1396" t="n">
@@ -39436,6 +43289,9 @@
           <t>(おねがい！)</t>
         </is>
       </c>
+      <c r="G1396" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="1397">
       <c r="A1397" t="n">
@@ -39462,6 +43318,9 @@
           <t>何しても</t>
         </is>
       </c>
+      <c r="G1397" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="1398">
       <c r="A1398" t="n">
@@ -39488,6 +43347,9 @@
           <t>どんな顔</t>
         </is>
       </c>
+      <c r="G1398" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="1399">
       <c r="A1399" t="n">
@@ -39514,6 +43376,9 @@
           <t>見せてても</t>
         </is>
       </c>
+      <c r="G1399" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="1400">
       <c r="A1400" t="n">
@@ -41440,6 +45305,9 @@
           <t>(いくぞ)</t>
         </is>
       </c>
+      <c r="G1472" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="1473">
       <c r="A1473" t="n">
@@ -41466,6 +45334,14 @@
           <t>(fu)</t>
         </is>
       </c>
+      <c r="G1473" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1473" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
     </row>
     <row r="1474">
       <c r="A1474" t="n">
@@ -41911,6 +45787,9 @@
           <t>大きな夢叶えるとき、</t>
         </is>
       </c>
+      <c r="G1490" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="1491">
       <c r="A1491" t="n">
@@ -41938,6 +45817,9 @@
 そういうことです</t>
         </is>
       </c>
+      <c r="G1491" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="1492">
       <c r="A1492" t="n">
@@ -42357,6 +46239,9 @@
           <t>小さな夢の始まりに、</t>
         </is>
       </c>
+      <c r="G1507" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="1508">
       <c r="A1508" t="n">
@@ -42384,6 +46269,9 @@
 そういうことです</t>
         </is>
       </c>
+      <c r="G1508" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="1509">
       <c r="A1509" t="n">
@@ -42516,6 +46404,9 @@
           <t>大きな夢叶えるとき、</t>
         </is>
       </c>
+      <c r="G1513" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="1514">
       <c r="A1514" t="n">
@@ -42543,6 +46434,9 @@
 そういうことです</t>
         </is>
       </c>
+      <c r="G1514" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="1515">
       <c r="A1515" t="n">
@@ -43092,6 +46986,9 @@
           <t>笑顔で探す</t>
         </is>
       </c>
+      <c r="G1535" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="1536">
       <c r="A1536" t="n">
@@ -43118,6 +47015,9 @@
           <t>そっちのほうが</t>
         </is>
       </c>
+      <c r="G1536" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="1537">
       <c r="A1537" t="n">
@@ -43144,6 +47044,9 @@
           <t>楽しいでしょ</t>
         </is>
       </c>
+      <c r="G1537" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="1538">
       <c r="A1538" t="n">
@@ -45061,6 +48964,9 @@
 向き合うこと教えてくれた</t>
         </is>
       </c>
+      <c r="G1610" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="1611">
       <c r="A1611" t="n">
@@ -45087,6 +48993,14 @@
           <t>見上げた　空は青く光る</t>
         </is>
       </c>
+      <c r="G1611" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1611" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
     </row>
     <row r="1612">
       <c r="A1612" t="n">
@@ -45244,6 +49158,9 @@
           <t>もっとずっと　描き続けるよ</t>
         </is>
       </c>
+      <c r="G1617" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="1618">
       <c r="A1618" t="n">
@@ -45271,6 +49188,14 @@
 瞬間　輝いた</t>
         </is>
       </c>
+      <c r="G1618" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1618" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
     </row>
     <row r="1619">
       <c r="A1619" t="n">
@@ -45350,6 +49275,9 @@
 口癖　挫けそうになっても</t>
         </is>
       </c>
+      <c r="G1621" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="1622">
       <c r="A1622" t="n">
@@ -45376,6 +49304,14 @@
           <t>光を辿れば　キミだった</t>
         </is>
       </c>
+      <c r="G1622" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1622" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
     </row>
     <row r="1623">
       <c r="A1623" t="n">
@@ -45532,6 +49468,9 @@
           <t>もっとずっと　描き続けるよ</t>
         </is>
       </c>
+      <c r="G1628" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="1629">
       <c r="A1629" t="n">
@@ -45558,6 +49497,14 @@
           <t>嘘じゃない　瞬間　輝いた</t>
         </is>
       </c>
+      <c r="G1629" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1629" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
     </row>
     <row r="1630">
       <c r="A1630" t="n">
@@ -45663,6 +49610,9 @@
           <t>何度も　何度も　何度も　何度も</t>
         </is>
       </c>
+      <c r="G1633" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="1634">
       <c r="A1634" t="n">
@@ -45689,6 +49639,14 @@
           <t>何度だって伝えるよ</t>
         </is>
       </c>
+      <c r="G1634" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1634" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
     </row>
     <row r="1635">
       <c r="A1635" t="n">
@@ -45767,6 +49725,9 @@
           <t>Ah　この両手に</t>
         </is>
       </c>
+      <c r="G1637" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="1638">
       <c r="A1638" t="n">
@@ -45793,6 +49754,14 @@
           <t>抱えきれないくらいの想いを</t>
         </is>
       </c>
+      <c r="G1638" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1638" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
     </row>
     <row r="1639">
       <c r="A1639" t="n">
@@ -45845,6 +49814,9 @@
           <t>もっとずっと　描き続けるよ</t>
         </is>
       </c>
+      <c r="G1640" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="1641">
       <c r="A1641" t="n">
@@ -45871,6 +49843,14 @@
           <t>嘘じゃない　瞬間　輝いた</t>
         </is>
       </c>
+      <c r="G1641" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1641" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
     </row>
     <row r="1642">
       <c r="A1642" t="n">
@@ -45924,6 +49904,9 @@
           <t>難しいって</t>
         </is>
       </c>
+      <c r="G1643" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="1644">
       <c r="A1644" t="n">
@@ -45950,6 +49933,14 @@
           <t>誰かは言うけれど</t>
         </is>
       </c>
+      <c r="G1644" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1644" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
     </row>
     <row r="1645">
       <c r="A1645" t="n">
@@ -46449,6 +50440,9 @@
           <t>そりゃそうです。</t>
         </is>
       </c>
+      <c r="G1663" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="1664">
       <c r="A1664" t="n">
@@ -46475,6 +50469,9 @@
           <t>こちとら人間なので。</t>
         </is>
       </c>
+      <c r="G1664" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="1665">
       <c r="A1665" t="n">
@@ -46529,6 +50526,9 @@
 ドドカンと</t>
         </is>
       </c>
+      <c r="G1666" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="1667">
       <c r="A1667" t="n">
@@ -46555,6 +50555,14 @@
           <t>めちゃドカンと</t>
         </is>
       </c>
+      <c r="G1667" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1667" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
     </row>
     <row r="1668">
       <c r="A1668" t="n">
@@ -46685,6 +50693,9 @@
           <t>エナジー溜めるし、</t>
         </is>
       </c>
+      <c r="G1672" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="1673">
       <c r="A1673" t="n">
@@ -46711,6 +50722,9 @@
           <t>大丈夫！</t>
         </is>
       </c>
+      <c r="G1673" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="1674">
       <c r="A1674" t="n">
@@ -47730,6 +51744,9 @@
           <t>だって、ちょっとくらいの</t>
         </is>
       </c>
+      <c r="G1712" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="1713">
       <c r="A1713" t="n">
@@ -47756,6 +51773,9 @@
           <t>マイナスもなきゃ</t>
         </is>
       </c>
+      <c r="G1713" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="1714">
       <c r="A1714" t="n">
@@ -47808,6 +51828,9 @@
           <t>まあね</t>
         </is>
       </c>
+      <c r="G1715" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="1716">
       <c r="A1716" t="n">
@@ -47834,6 +51857,9 @@
           <t>こんなに幸せでいいのです(いいのです)</t>
         </is>
       </c>
+      <c r="G1716" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="1717">
       <c r="A1717" t="n">
@@ -47886,6 +51912,9 @@
           <t>いぬはかけまわり、</t>
         </is>
       </c>
+      <c r="G1718" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="1719">
       <c r="A1719" t="n">
@@ -47912,6 +51941,9 @@
           <t>ねこはかわいいし</t>
         </is>
       </c>
+      <c r="G1719" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="1720">
       <c r="A1720" t="n">
@@ -48330,6 +52362,9 @@
           <t>だって、ちょっとくらいの</t>
         </is>
       </c>
+      <c r="G1735" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="1736">
       <c r="A1736" t="n">
@@ -48356,6 +52391,9 @@
           <t>試練とかもなきゃ</t>
         </is>
       </c>
+      <c r="G1736" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="1737">
       <c r="A1737" t="n">
@@ -48408,6 +52446,9 @@
           <t>まあね</t>
         </is>
       </c>
+      <c r="G1738" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="1739">
       <c r="A1739" t="n">
@@ -48434,6 +52475,9 @@
           <t>結局幸せでいいのです(いいのです)</t>
         </is>
       </c>
+      <c r="G1739" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="1740">
       <c r="A1740" t="n">
@@ -48486,6 +52530,9 @@
           <t>おみこしにのって、</t>
         </is>
       </c>
+      <c r="G1741" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="1742">
       <c r="A1742" t="n">
@@ -48512,6 +52559,9 @@
           <t>花火もあげて</t>
         </is>
       </c>
+      <c r="G1742" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="1743">
       <c r="A1743" t="n">
@@ -48694,6 +52744,9 @@
           <t>だって、ちょっとくらいの</t>
         </is>
       </c>
+      <c r="G1749" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="1750">
       <c r="A1750" t="n">
@@ -48720,6 +52773,9 @@
           <t>マイナスもなきゃ</t>
         </is>
       </c>
+      <c r="G1750" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="1751">
       <c r="A1751" t="n">
@@ -48772,6 +52828,9 @@
           <t>まあね</t>
         </is>
       </c>
+      <c r="G1752" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="1753">
       <c r="A1753" t="n">
@@ -48798,6 +52857,9 @@
           <t>こんなに幸せでいいのです(いいのです)</t>
         </is>
       </c>
+      <c r="G1753" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="1754">
       <c r="A1754" t="n">
@@ -48850,6 +52912,9 @@
           <t>いぬはかけまわり、</t>
         </is>
       </c>
+      <c r="G1755" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="1756">
       <c r="A1756" t="n">
@@ -48876,6 +52941,9 @@
           <t>ねこはかわいいし</t>
         </is>
       </c>
+      <c r="G1756" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="1757">
       <c r="A1757" t="n">
@@ -48954,6 +53022,9 @@
           <t>最高の今に、</t>
         </is>
       </c>
+      <c r="G1759" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="1760">
       <c r="A1760" t="n">
@@ -48980,6 +53051,9 @@
           <t>おめでとうだよ！</t>
         </is>
       </c>
+      <c r="G1760" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="1761">
       <c r="A1761" t="n">
@@ -49269,6 +53343,9 @@
           <t>前髪は拘りの見せ所だし</t>
         </is>
       </c>
+      <c r="G1771" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="1772">
       <c r="A1772" t="n">
@@ -49295,6 +53372,9 @@
           <t>(いのち笑)</t>
         </is>
       </c>
+      <c r="G1772" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="1773">
       <c r="A1773" t="n">
@@ -49636,6 +53716,9 @@
           <t>ノー</t>
         </is>
       </c>
+      <c r="G1785" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="1786">
       <c r="A1786" t="n">
@@ -49662,6 +53745,9 @@
           <t>ノー</t>
         </is>
       </c>
+      <c r="G1786" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="1787">
       <c r="A1787" t="n">
@@ -49688,6 +53774,9 @@
           <t>ノー</t>
         </is>
       </c>
+      <c r="G1787" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="1788">
       <c r="A1788" t="n">
@@ -52900,6 +56989,9 @@
 そう有能</t>
         </is>
       </c>
+      <c r="G1909" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="1910">
       <c r="A1910" t="n">
@@ -52925,6 +57017,14 @@
         <is>
           <t>カッティン　カッティン
 アソびましょ</t>
+        </is>
+      </c>
+      <c r="G1910" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1910" t="inlineStr">
+        <is>
+          <t>full</t>
         </is>
       </c>
     </row>
